--- a/sources/heihachi_step7.xlsx
+++ b/sources/heihachi_step7.xlsx
@@ -417,13 +417,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA97"/>
+  <dimension ref="A1:AB97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
     <col width="25" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="29" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
     <col width="56" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="7" customWidth="1" min="7" max="7"/>
@@ -443,10 +443,11 @@
     <col width="14" customWidth="1" min="21" max="21"/>
     <col width="13" customWidth="1" min="22" max="22"/>
     <col width="200" customWidth="1" min="23" max="23"/>
-    <col width="38" customWidth="1" min="24" max="24"/>
+    <col width="10" customWidth="1" min="24" max="24"/>
     <col width="38" customWidth="1" min="25" max="25"/>
     <col width="38" customWidth="1" min="26" max="26"/>
-    <col width="11" customWidth="1" min="27" max="27"/>
+    <col width="38" customWidth="1" min="27" max="27"/>
+    <col width="11" customWidth="1" min="28" max="28"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -574,20 +575,25 @@
       </c>
       <c r="X2" s="1" t="inlineStr">
         <is>
+          <t>Taggable</t>
+        </is>
+      </c>
+      <c r="Y2" s="1" t="inlineStr">
+        <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="Y2" s="1" t="inlineStr">
+      <c r="Z2" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="Z2" s="1" t="inlineStr">
+      <c r="AA2" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="AA2" s="1" t="inlineStr">
+      <c r="AB2" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
@@ -649,12 +655,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>055edf24-00e6-4bb3-8ff4-9113ed584c70</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t>6ad36a17-e53f-4652-ac7e-4de4d45e451e</t>
         </is>
@@ -716,12 +722,12 @@
           <t>2</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>2a7efd25-998a-4518-b8b6-0ec6345106a4</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
+      <c r="Z4" t="inlineStr">
         <is>
           <t>522a334c-eb72-43e3-881e-74f4b50d8530</t>
         </is>
@@ -730,22 +736,22 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>f,f+1+2 [~5]</t>
+          <t>f,f+1+2</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>f,f+1+2 [~5]</t>
+          <t>f,f+1+2</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Stone Head [Tag]</t>
+          <t>Stone Head</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Stone Head [Tag]</t>
+          <t>Stone Head</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -790,10 +796,15 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
           <t>e115e974-d648-4855-89a2-19c755a06698</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
+      <c r="Z5" t="inlineStr">
         <is>
           <t>92ac3627-b2f3-45a8-8ce2-b2bfc7764f09</t>
         </is>
@@ -860,12 +871,12 @@
           <t>Only against Jin, Heihachi, Lei, Kazuya, Jack-2, Gun Jack and Prototype Jack. They can reverse with 1 or 2. Heihachi can reverse again with 1+2, continuing back and forth. Damage is 42 against Kuma.</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>5fa5155a-0eba-4d3f-b813-a27edfe0bf4a</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
+      <c r="Z6" t="inlineStr">
         <is>
           <t>de8b4335-3cff-441f-aa66-9a78e87974b6</t>
         </is>
@@ -922,12 +933,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
+      <c r="Z7" t="inlineStr">
         <is>
           <t>f46ce297-20aa-42e9-8fad-54b3f4704d3d</t>
         </is>
       </c>
-      <c r="AA7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -984,12 +995,12 @@
           <t>2</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>2bed6e68-3dcb-46ce-8b44-5a8ab9825180</t>
         </is>
       </c>
-      <c r="AA8" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -1046,12 +1057,12 @@
           <t>None</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
+      <c r="Z9" t="inlineStr">
         <is>
           <t>94e89bd5-df08-4d1f-954d-ff55d170def7</t>
         </is>
       </c>
-      <c r="AA9" t="inlineStr">
+      <c r="AB9" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -1183,20 +1194,25 @@
       </c>
       <c r="X12" s="1" t="inlineStr">
         <is>
+          <t>Taggable</t>
+        </is>
+      </c>
+      <c r="Y12" s="1" t="inlineStr">
+        <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="Y12" s="1" t="inlineStr">
+      <c r="Z12" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="Z12" s="1" t="inlineStr">
+      <c r="AA12" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="AA12" s="1" t="inlineStr">
+      <c r="AB12" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
@@ -1278,12 +1294,12 @@
           <t>h</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr">
+      <c r="Y13" t="inlineStr">
         <is>
           <t>29f05378-4c42-41a0-a55f-5cc9bca80f34</t>
         </is>
       </c>
-      <c r="Y13" t="inlineStr">
+      <c r="Z13" t="inlineStr">
         <is>
           <t>a5a49b2d-da7e-44d1-9b17-38b7637f3a08</t>
         </is>
@@ -1365,12 +1381,12 @@
           <t>h</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr">
+      <c r="Y14" t="inlineStr">
         <is>
           <t>61030085-8620-468e-a73d-e20eff055cfd</t>
         </is>
       </c>
-      <c r="Y14" t="inlineStr">
+      <c r="Z14" t="inlineStr">
         <is>
           <t>ad1f150e-9eae-4e89-ac2b-5f5fa8a4b89e</t>
         </is>
@@ -1452,12 +1468,12 @@
           <t>h</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
+      <c r="Y15" t="inlineStr">
         <is>
           <t>ceaf0b9e-1026-4ae7-bba1-dce4c65e1b37</t>
         </is>
       </c>
-      <c r="Y15" t="inlineStr">
+      <c r="Z15" t="inlineStr">
         <is>
           <t>27e5cf01-5d6e-4d54-943e-97082c4f15a6</t>
         </is>
@@ -1539,12 +1555,12 @@
           <t>h</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr">
+      <c r="Y16" t="inlineStr">
         <is>
           <t>f1d52cca-9dbb-4d7d-8b37-abe411e415a3</t>
         </is>
       </c>
-      <c r="Y16" t="inlineStr">
+      <c r="Z16" t="inlineStr">
         <is>
           <t>e171489f-567f-4d95-acb0-794681c07d75</t>
         </is>
@@ -1626,12 +1642,12 @@
           <t>h</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr">
+      <c r="Y17" t="inlineStr">
         <is>
           <t>151a093a-4a24-4707-9fdc-85ae0ae9d089</t>
         </is>
       </c>
-      <c r="Y17" t="inlineStr">
+      <c r="Z17" t="inlineStr">
         <is>
           <t>5ee993a8-3ec1-4892-be2b-2d1dc4b43c29</t>
         </is>
@@ -1713,12 +1729,12 @@
           <t>h</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr">
+      <c r="Y18" t="inlineStr">
         <is>
           <t>eb144a38-b7da-49ec-8e96-85c4769df844</t>
         </is>
       </c>
-      <c r="Y18" t="inlineStr">
+      <c r="Z18" t="inlineStr">
         <is>
           <t>a29ab714-ffc6-4f5c-9549-2b5d2984c5b1</t>
         </is>
@@ -1800,12 +1816,12 @@
           <t>h</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr">
+      <c r="Y19" t="inlineStr">
         <is>
           <t>b885f59d-33f7-4aa4-b758-c5d018dbbefa</t>
         </is>
       </c>
-      <c r="Y19" t="inlineStr">
+      <c r="Z19" t="inlineStr">
         <is>
           <t>b09b5581-7097-4941-a01f-0eabfd91442f</t>
         </is>
@@ -1887,12 +1903,12 @@
           <t>h</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr">
+      <c r="Y20" t="inlineStr">
         <is>
           <t>8662a3d8-6f93-4295-bbbe-b15e2ce515b5</t>
         </is>
       </c>
-      <c r="Y20" t="inlineStr">
+      <c r="Z20" t="inlineStr">
         <is>
           <t>f23dc020-3cbc-46ec-9ff6-9f6942d0b908</t>
         </is>
@@ -1974,12 +1990,12 @@
           <t>m</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr">
+      <c r="Y21" t="inlineStr">
         <is>
           <t>30df2932-071a-443e-b19f-649d3a9c0960</t>
         </is>
       </c>
-      <c r="Y21" t="inlineStr">
+      <c r="Z21" t="inlineStr">
         <is>
           <t>87d16cd4-ad18-401f-96d2-f66948f7f066</t>
         </is>
@@ -2061,12 +2077,12 @@
           <t>s</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr">
+      <c r="Y22" t="inlineStr">
         <is>
           <t>4911413b-5c5a-46d9-969b-975b22762247</t>
         </is>
       </c>
-      <c r="Y22" t="inlineStr">
+      <c r="Z22" t="inlineStr">
         <is>
           <t>bd7b7be9-b98f-4a2f-a697-9726f37d7f29</t>
         </is>
@@ -2148,12 +2164,12 @@
           <t>l</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr">
+      <c r="Y23" t="inlineStr">
         <is>
           <t>c833b466-b036-4bac-a0b6-71c87f3b2e5d</t>
         </is>
       </c>
-      <c r="Y23" t="inlineStr">
+      <c r="Z23" t="inlineStr">
         <is>
           <t>751d7427-8654-498e-b79d-bc0d285469f4</t>
         </is>
@@ -2235,12 +2251,12 @@
           <t>l</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr">
+      <c r="Y24" t="inlineStr">
         <is>
           <t>5e8a47cc-f2d6-4273-8a70-4329b9604c1e</t>
         </is>
       </c>
-      <c r="Y24" t="inlineStr">
+      <c r="Z24" t="inlineStr">
         <is>
           <t>f649446d-5c13-4cb1-892b-9e55345cca38</t>
         </is>
@@ -2322,12 +2338,12 @@
           <t>s</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr">
+      <c r="Y25" t="inlineStr">
         <is>
           <t>9900670c-8afe-4c73-a313-1cb75c1bce79</t>
         </is>
       </c>
-      <c r="Y25" t="inlineStr">
+      <c r="Z25" t="inlineStr">
         <is>
           <t>fae825e3-99c8-440a-955e-2a814ff27735</t>
         </is>
@@ -2409,12 +2425,12 @@
           <t>s</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr">
+      <c r="Y26" t="inlineStr">
         <is>
           <t>90023022-398a-4423-833a-ba875bdfe248</t>
         </is>
       </c>
-      <c r="Y26" t="inlineStr">
+      <c r="Z26" t="inlineStr">
         <is>
           <t>5f9c0cb6-4f0f-443b-9d4b-2d9dc2782022</t>
         </is>
@@ -2496,12 +2512,12 @@
           <t>l</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr">
+      <c r="Y27" t="inlineStr">
         <is>
           <t>053a1ac4-73a0-4cb9-8dac-87ff3bc99058</t>
         </is>
       </c>
-      <c r="Y27" t="inlineStr">
+      <c r="Z27" t="inlineStr">
         <is>
           <t>3498e460-1be1-4a5f-8714-abecbeefce3b</t>
         </is>
@@ -2583,12 +2599,12 @@
           <t>l</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr">
+      <c r="Y28" t="inlineStr">
         <is>
           <t>3961163a-e7d3-4791-a056-23f7b4a65ce1</t>
         </is>
       </c>
-      <c r="Y28" t="inlineStr">
+      <c r="Z28" t="inlineStr">
         <is>
           <t>e73d65a4-ac30-47c9-962e-2a9034080fa4</t>
         </is>
@@ -2670,12 +2686,12 @@
           <t>m</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr">
+      <c r="Y29" t="inlineStr">
         <is>
           <t>ff808c39-0942-4f29-9af2-0c1d8937368c</t>
         </is>
       </c>
-      <c r="Y29" t="inlineStr">
+      <c r="Z29" t="inlineStr">
         <is>
           <t>a2218298-0d90-488a-ba7e-1c61827a703e</t>
         </is>
@@ -2757,12 +2773,12 @@
           <t>m</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr">
+      <c r="Y30" t="inlineStr">
         <is>
           <t>732d91c7-ae81-435c-ba3e-709873e67d97</t>
         </is>
       </c>
-      <c r="Y30" t="inlineStr">
+      <c r="Z30" t="inlineStr">
         <is>
           <t>f6367452-5e87-464f-9b47-d20b42453746</t>
         </is>
@@ -2844,12 +2860,12 @@
           <t>m</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr">
+      <c r="Y31" t="inlineStr">
         <is>
           <t>317dcdb4-06ab-4843-b04c-6f6653f87ad9</t>
         </is>
       </c>
-      <c r="Y31" t="inlineStr">
+      <c r="Z31" t="inlineStr">
         <is>
           <t>3884d910-0287-4c6d-ac21-d5039a604305</t>
         </is>
@@ -2931,12 +2947,12 @@
           <t>m</t>
         </is>
       </c>
-      <c r="X32" t="inlineStr">
+      <c r="Y32" t="inlineStr">
         <is>
           <t>996d2223-e5ac-4917-ac11-bdda927a8fa9</t>
         </is>
       </c>
-      <c r="Y32" t="inlineStr">
+      <c r="Z32" t="inlineStr">
         <is>
           <t>494df9c0-dd89-4489-a417-6d6480d86ea5</t>
         </is>
@@ -3018,12 +3034,12 @@
           <t>m</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr">
+      <c r="Y33" t="inlineStr">
         <is>
           <t>532a8f4f-8179-47ad-8f5e-cd79cbcb2d38</t>
         </is>
       </c>
-      <c r="Y33" t="inlineStr">
+      <c r="Z33" t="inlineStr">
         <is>
           <t>f07eb2c7-fa12-4dbe-bab0-c9f9b5a75c14</t>
         </is>
@@ -3105,12 +3121,12 @@
           <t>m</t>
         </is>
       </c>
-      <c r="X34" t="inlineStr">
+      <c r="Y34" t="inlineStr">
         <is>
           <t>03e7a494-42af-4c02-ae04-fe6e3d544130</t>
         </is>
       </c>
-      <c r="Y34" t="inlineStr">
+      <c r="Z34" t="inlineStr">
         <is>
           <t>4bb45d34-7291-4b69-bd2f-a93895a01886</t>
         </is>
@@ -3192,12 +3208,12 @@
           <t>m</t>
         </is>
       </c>
-      <c r="X35" t="inlineStr">
+      <c r="Y35" t="inlineStr">
         <is>
           <t>b6b2bbe2-54ac-4521-8e16-8e4164acccfb</t>
         </is>
       </c>
-      <c r="Y35" t="inlineStr">
+      <c r="Z35" t="inlineStr">
         <is>
           <t>d6106ca6-1e22-46b5-aa2c-c273dcfd0c04</t>
         </is>
@@ -3279,12 +3295,12 @@
           <t>m</t>
         </is>
       </c>
-      <c r="X36" t="inlineStr">
+      <c r="Y36" t="inlineStr">
         <is>
           <t>c02d47de-47e8-4faa-9ada-5b2889324555</t>
         </is>
       </c>
-      <c r="Y36" t="inlineStr">
+      <c r="Z36" t="inlineStr">
         <is>
           <t>bf5265d6-4a33-4218-b469-1af5406c7075</t>
         </is>
@@ -3416,20 +3432,25 @@
       </c>
       <c r="X39" s="1" t="inlineStr">
         <is>
+          <t>Taggable</t>
+        </is>
+      </c>
+      <c r="Y39" s="1" t="inlineStr">
+        <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="Y39" s="1" t="inlineStr">
+      <c r="Z39" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="Z39" s="1" t="inlineStr">
+      <c r="AA39" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="AA39" s="1" t="inlineStr">
+      <c r="AB39" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
@@ -3526,12 +3547,12 @@
           <t>KSc KSco GB</t>
         </is>
       </c>
-      <c r="X40" t="inlineStr">
+      <c r="Y40" t="inlineStr">
         <is>
           <t>ae5886ed-653a-48be-b9c7-15ef4aacda57</t>
         </is>
       </c>
-      <c r="Y40" t="inlineStr">
+      <c r="Z40" t="inlineStr">
         <is>
           <t>273d9ede-8672-4cea-8b4a-9b17f83ef955</t>
         </is>
@@ -3623,12 +3644,12 @@
           <t>hh</t>
         </is>
       </c>
-      <c r="X41" t="inlineStr">
+      <c r="Y41" t="inlineStr">
         <is>
           <t>c28a50b0-4d64-4d99-af29-2092c90c0512</t>
         </is>
       </c>
-      <c r="Y41" t="inlineStr">
+      <c r="Z41" t="inlineStr">
         <is>
           <t>c1cf7b8f-c486-4fef-96b7-5a636bbc6b41</t>
         </is>
@@ -3720,17 +3741,17 @@
           <t>CSc</t>
         </is>
       </c>
-      <c r="X42" t="inlineStr">
+      <c r="Y42" t="inlineStr">
         <is>
           <t>ce7b2f27-c16a-4507-b110-dd9638bb5ade</t>
         </is>
       </c>
-      <c r="Y42" t="inlineStr">
+      <c r="Z42" t="inlineStr">
         <is>
           <t>d5ead6e5-b493-4f13-a54e-e9a86228b0a1</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
+      <c r="AA42" t="inlineStr">
         <is>
           <t>c28a50b0-4d64-4d99-af29-2092c90c0512</t>
         </is>
@@ -3822,12 +3843,12 @@
           <t>hhm</t>
         </is>
       </c>
-      <c r="X43" t="inlineStr">
+      <c r="Y43" t="inlineStr">
         <is>
           <t>5a1a5efc-057d-4db1-97bf-1013a5f7eb7d</t>
         </is>
       </c>
-      <c r="Y43" t="inlineStr">
+      <c r="Z43" t="inlineStr">
         <is>
           <t>4c02bf2e-9cdb-4b12-813c-2e5cad3aa246</t>
         </is>
@@ -3919,12 +3940,12 @@
           <t>hhh</t>
         </is>
       </c>
-      <c r="X44" t="inlineStr">
+      <c r="Y44" t="inlineStr">
         <is>
           <t>84232fe2-22f5-45db-88bb-eef3f04153de</t>
         </is>
       </c>
-      <c r="Y44" t="inlineStr">
+      <c r="Z44" t="inlineStr">
         <is>
           <t>6d0a6ef4-5dc4-42d5-bede-4afc6032e41e</t>
         </is>
@@ -4021,17 +4042,17 @@
           <t>Demon Executioner cancels the previous hit.; The Side Step cancels the Demon Executioner.</t>
         </is>
       </c>
-      <c r="X45" t="inlineStr">
+      <c r="Y45" t="inlineStr">
         <is>
           <t>5b09c08e-09b3-4913-88a3-14d3bf367ca9</t>
         </is>
       </c>
-      <c r="Y45" t="inlineStr">
+      <c r="Z45" t="inlineStr">
         <is>
           <t>d179dfe4-126b-45c6-891e-6a2914df58cf</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
+      <c r="AA45" t="inlineStr">
         <is>
           <t>84232fe2-22f5-45db-88bb-eef3f04153de</t>
         </is>
@@ -4123,12 +4144,12 @@
           <t>hmm</t>
         </is>
       </c>
-      <c r="X46" t="inlineStr">
+      <c r="Y46" t="inlineStr">
         <is>
           <t>cf18e825-afa4-4f63-a13b-ab9f82dd60d8</t>
         </is>
       </c>
-      <c r="Y46" t="inlineStr">
+      <c r="Z46" t="inlineStr">
         <is>
           <t>ba68e2af-947f-46fd-bbd4-6f9748de5fa6</t>
         </is>
@@ -4225,12 +4246,12 @@
           <t>GB</t>
         </is>
       </c>
-      <c r="X47" t="inlineStr">
+      <c r="Y47" t="inlineStr">
         <is>
           <t>25172e0e-0977-4665-a19b-f6b673165143</t>
         </is>
       </c>
-      <c r="Y47" t="inlineStr">
+      <c r="Z47" t="inlineStr">
         <is>
           <t>ed33786a-081d-4f6b-a2b4-21493b6d9ec4</t>
         </is>
@@ -4322,12 +4343,12 @@
           <t>m</t>
         </is>
       </c>
-      <c r="X48" t="inlineStr">
+      <c r="Y48" t="inlineStr">
         <is>
           <t>dfd7ff87-faaf-4127-bbd9-4dca53b7da21</t>
         </is>
       </c>
-      <c r="Y48" t="inlineStr">
+      <c r="Z48" t="inlineStr">
         <is>
           <t>3dabca7e-8c1b-4b08-a5df-10b49c3ed200</t>
         </is>
@@ -4414,17 +4435,17 @@
           <t>mm</t>
         </is>
       </c>
-      <c r="X49" t="inlineStr">
+      <c r="Y49" t="inlineStr">
         <is>
           <t>8ce5cdd0-9ea6-4f83-8b25-9d0afc9413a0</t>
         </is>
       </c>
-      <c r="Y49" t="inlineStr">
+      <c r="Z49" t="inlineStr">
         <is>
           <t>7c6c71d8-5c87-4940-ad23-38ed00f6149f</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
+      <c r="AA49" t="inlineStr">
         <is>
           <t>dfd7ff87-faaf-4127-bbd9-4dca53b7da21</t>
         </is>
@@ -4433,22 +4454,22 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>df+1,2 [~5]</t>
+          <t>df+1,2</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>df+1,2 [~5]</t>
+          <t>df+1,2</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Twin Pistons [Tag]</t>
+          <t>Twin Pistons</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Twin Pistons [Tag]</t>
+          <t>Twin Pistons</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -4523,10 +4544,15 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
           <t>ec5ebcd7-e9bc-44b1-9b77-b91f9dc39f66</t>
         </is>
       </c>
-      <c r="Y50" t="inlineStr">
+      <c r="Z50" t="inlineStr">
         <is>
           <t>7cca0613-8eba-4b47-8c55-6bacc4cf6858</t>
         </is>
@@ -4623,12 +4649,12 @@
           <t>On a clean hit damage is 52.</t>
         </is>
       </c>
-      <c r="X51" t="inlineStr">
+      <c r="Y51" t="inlineStr">
         <is>
           <t>fc9f67f0-efd6-442f-a3dd-40673e0f9273</t>
         </is>
       </c>
-      <c r="Y51" t="inlineStr">
+      <c r="Z51" t="inlineStr">
         <is>
           <t>e7f4b372-4384-43b9-9041-5008424e98fc</t>
         </is>
@@ -4725,12 +4751,12 @@
           <t>CF KNDc</t>
         </is>
       </c>
-      <c r="X52" t="inlineStr">
+      <c r="Y52" t="inlineStr">
         <is>
           <t>03aed9fd-acbe-4903-a5f4-86fee6b288eb</t>
         </is>
       </c>
-      <c r="Y52" t="inlineStr">
+      <c r="Z52" t="inlineStr">
         <is>
           <t>52f48595-1a7d-43df-984b-9aa5af0acbe8</t>
         </is>
@@ -4827,12 +4853,12 @@
           <t>MS KNDc</t>
         </is>
       </c>
-      <c r="X53" t="inlineStr">
+      <c r="Y53" t="inlineStr">
         <is>
           <t>53f9e49f-94f7-4e5b-8dca-5cc758b156e9</t>
         </is>
       </c>
-      <c r="Y53" t="inlineStr">
+      <c r="Z53" t="inlineStr">
         <is>
           <t>95ab05b1-eee0-4967-802f-5ec8701cd87e</t>
         </is>
@@ -4924,12 +4950,12 @@
           <t>hh</t>
         </is>
       </c>
-      <c r="X54" t="inlineStr">
+      <c r="Y54" t="inlineStr">
         <is>
           <t>0a027bcb-93fd-4ff0-8ccf-f195fc7eff06</t>
         </is>
       </c>
-      <c r="Y54" t="inlineStr">
+      <c r="Z54" t="inlineStr">
         <is>
           <t>d1e026ec-e70f-4352-ac90-f4a4d9bd194a</t>
         </is>
@@ -5021,12 +5047,12 @@
           <t>h</t>
         </is>
       </c>
-      <c r="X55" t="inlineStr">
+      <c r="Y55" t="inlineStr">
         <is>
           <t>def5efd8-0361-461e-ba4d-56503556be0d</t>
         </is>
       </c>
-      <c r="Y55" t="inlineStr">
+      <c r="Z55" t="inlineStr">
         <is>
           <t>114d3f24-d4a3-480e-99f9-4ccee1b5e132</t>
         </is>
@@ -5128,17 +5154,17 @@
           <t>Demon Executioner cancels the previous hit.</t>
         </is>
       </c>
-      <c r="X56" t="inlineStr">
+      <c r="Y56" t="inlineStr">
         <is>
           <t>6bc7980e-339b-4862-a189-7a7c97ad654b</t>
         </is>
       </c>
-      <c r="Y56" t="inlineStr">
+      <c r="Z56" t="inlineStr">
         <is>
           <t>52149449-5e95-4e94-ae94-d23c918581ec</t>
         </is>
       </c>
-      <c r="Z56" t="inlineStr">
+      <c r="AA56" t="inlineStr">
         <is>
           <t>def5efd8-0361-461e-ba4d-56503556be0d</t>
         </is>
@@ -5147,22 +5173,22 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>f,f+2 [~5]</t>
+          <t>f,f+2</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>f,f+2 [~5]</t>
+          <t>f,f+2</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Demon Godfist [Tag]</t>
+          <t>Demon Godfist</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Demon Godfist [Tag]</t>
+          <t>Demon Godfist</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -5237,10 +5263,15 @@
       </c>
       <c r="X57" t="inlineStr">
         <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
           <t>7e41126e-b556-4341-90e6-de9a17e27e63</t>
         </is>
       </c>
-      <c r="Y57" t="inlineStr">
+      <c r="Z57" t="inlineStr">
         <is>
           <t>d757091e-2404-4579-8d58-622845ab4257</t>
         </is>
@@ -5249,22 +5280,22 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>f,N,d,df+2 [~5]</t>
+          <t>f,N,d,df+2</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>f,N,d,df+2 [~5]</t>
+          <t>f,N,d,df+2</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Wind Godfist [Tag]</t>
+          <t>Wind Godfist</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Wind Godfist [Tag]</t>
+          <t>Wind Godfist</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -5339,10 +5370,15 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
           <t>e9cc8d24-94c5-4666-904c-ce10afa52191</t>
         </is>
       </c>
-      <c r="Y58" t="inlineStr">
+      <c r="Z58" t="inlineStr">
         <is>
           <t>38165070-f819-4dee-a042-75a435e0973a</t>
         </is>
@@ -5351,22 +5387,22 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>f~N~d~df+2 [~5]</t>
+          <t>f~N~d~df+2</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>f~N~d~df+2 [~5]</t>
+          <t>f~N~d~df+2</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Electric Wind Godfist [Tag]</t>
+          <t>Electric Wind Godfist</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Electric Wind Godfist [Tag]</t>
+          <t>Electric Wind Godfist</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -5441,10 +5477,15 @@
       </c>
       <c r="X59" t="inlineStr">
         <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
           <t>ca860141-c30a-4429-bc3f-ee8db6a8c1c4</t>
         </is>
       </c>
-      <c r="Y59" t="inlineStr">
+      <c r="Z59" t="inlineStr">
         <is>
           <t>6830a895-2438-4045-8b3c-c8372219b444</t>
         </is>
@@ -5536,12 +5577,12 @@
           <t>m</t>
         </is>
       </c>
-      <c r="X60" t="inlineStr">
+      <c r="Y60" t="inlineStr">
         <is>
           <t>93bd464b-add8-4400-9fa2-07651b194151</t>
         </is>
       </c>
-      <c r="Y60" t="inlineStr">
+      <c r="Z60" t="inlineStr">
         <is>
           <t>1ac6d532-3b56-49ac-a240-b0459bec630a</t>
         </is>
@@ -5638,12 +5679,12 @@
           <t>MS CSc</t>
         </is>
       </c>
-      <c r="X61" t="inlineStr">
+      <c r="Y61" t="inlineStr">
         <is>
           <t>5ea71dae-6d6f-4d22-a793-286c4e016413</t>
         </is>
       </c>
-      <c r="Y61" t="inlineStr">
+      <c r="Z61" t="inlineStr">
         <is>
           <t>cabb429b-8362-45b7-936e-5184c726b303</t>
         </is>
@@ -5740,12 +5781,12 @@
           <t>GB</t>
         </is>
       </c>
-      <c r="X62" t="inlineStr">
+      <c r="Y62" t="inlineStr">
         <is>
           <t>fc8a8eb1-ad44-4894-8dbe-7ef55b382149</t>
         </is>
       </c>
-      <c r="Y62" t="inlineStr">
+      <c r="Z62" t="inlineStr">
         <is>
           <t>20da6fcd-32b8-4d8f-8cb5-1fe9f89db475</t>
         </is>
@@ -5847,12 +5888,12 @@
           <t>GB</t>
         </is>
       </c>
-      <c r="X63" t="inlineStr">
+      <c r="Y63" t="inlineStr">
         <is>
           <t>19d63d7e-c9fa-4752-b05b-1568ef1eff12</t>
         </is>
       </c>
-      <c r="Y63" t="inlineStr">
+      <c r="Z63" t="inlineStr">
         <is>
           <t>292e8322-a299-4d25-9f86-079da27de238</t>
         </is>
@@ -5949,12 +5990,12 @@
           <t>GB</t>
         </is>
       </c>
-      <c r="X64" t="inlineStr">
+      <c r="Y64" t="inlineStr">
         <is>
           <t>4021c60b-e178-47a2-89e4-4cfa7ca28e40</t>
         </is>
       </c>
-      <c r="Y64" t="inlineStr">
+      <c r="Z64" t="inlineStr">
         <is>
           <t>2f13ea2c-55ea-482d-aefb-3221ba69b317</t>
         </is>
@@ -6046,12 +6087,12 @@
           <t>L</t>
         </is>
       </c>
-      <c r="X65" t="inlineStr">
+      <c r="Y65" t="inlineStr">
         <is>
           <t>c3570215-9bb3-404f-b1e9-756b8c8580bb</t>
         </is>
       </c>
-      <c r="Y65" t="inlineStr">
+      <c r="Z65" t="inlineStr">
         <is>
           <t>eceddea0-38d0-46b1-852b-31320d807156</t>
         </is>
@@ -6153,12 +6194,12 @@
           <t>On neutral block the 2nd hit will connect.</t>
         </is>
       </c>
-      <c r="X66" t="inlineStr">
+      <c r="Y66" t="inlineStr">
         <is>
           <t>9e590449-e10d-4d5e-a302-010249025523</t>
         </is>
       </c>
-      <c r="Y66" t="inlineStr">
+      <c r="Z66" t="inlineStr">
         <is>
           <t>cb2e07ce-106c-40a9-bc4e-a63422db65e8</t>
         </is>
@@ -6215,12 +6256,12 @@
           <t>JG</t>
         </is>
       </c>
-      <c r="X67" t="inlineStr">
+      <c r="Y67" t="inlineStr">
         <is>
           <t>871b2c24-ff65-4e92-b6e1-44b2616547a8</t>
         </is>
       </c>
-      <c r="Y67" t="inlineStr">
+      <c r="Z67" t="inlineStr">
         <is>
           <t>69de16a3-4a9e-40f4-ad50-e92f48c505db</t>
         </is>
@@ -6312,12 +6353,12 @@
           <t>hL</t>
         </is>
       </c>
-      <c r="X68" t="inlineStr">
+      <c r="Y68" t="inlineStr">
         <is>
           <t>6df4b756-97b1-4fcf-b8ff-a29527737049</t>
         </is>
       </c>
-      <c r="Y68" t="inlineStr">
+      <c r="Z68" t="inlineStr">
         <is>
           <t>e2b554ce-7879-4d5d-9a63-0ff018f5d5ef</t>
         </is>
@@ -6414,12 +6455,12 @@
           <t>mm</t>
         </is>
       </c>
-      <c r="X69" t="inlineStr">
+      <c r="Y69" t="inlineStr">
         <is>
           <t>e76e6c9a-0442-440c-883d-38289c144dd6</t>
         </is>
       </c>
-      <c r="Y69" t="inlineStr">
+      <c r="Z69" t="inlineStr">
         <is>
           <t>2acd50c8-1536-44db-bd07-34af0327aeda</t>
         </is>
@@ -6521,12 +6562,12 @@
           <t>The Hell Sweeps causes Knee Drop Stun, you can still block the next Hell Sweep. Causing Heihachi to Low Block Stagger.</t>
         </is>
       </c>
-      <c r="X70" t="inlineStr">
+      <c r="Y70" t="inlineStr">
         <is>
           <t>671ef239-098f-4d0b-bfd2-166912e226ae</t>
         </is>
       </c>
-      <c r="Y70" t="inlineStr">
+      <c r="Z70" t="inlineStr">
         <is>
           <t>e8203366-e9e8-438e-b327-bfc5e0436bff</t>
         </is>
@@ -6598,17 +6639,17 @@
           <t>Lm</t>
         </is>
       </c>
-      <c r="X71" t="inlineStr">
+      <c r="Y71" t="inlineStr">
         <is>
           <t>98628fce-5a47-4ba1-a41a-f455273494d4</t>
         </is>
       </c>
-      <c r="Y71" t="inlineStr">
+      <c r="Z71" t="inlineStr">
         <is>
           <t>1fb2c0d5-9f21-48d7-8e53-43577238f9ad</t>
         </is>
       </c>
-      <c r="Z71" t="inlineStr">
+      <c r="AA71" t="inlineStr">
         <is>
           <t>671ef239-098f-4d0b-bfd2-166912e226ae</t>
         </is>
@@ -6695,17 +6736,17 @@
           <t>Lmm</t>
         </is>
       </c>
-      <c r="X72" t="inlineStr">
+      <c r="Y72" t="inlineStr">
         <is>
           <t>f9614d72-ba63-4105-a42b-1bcf84c119a2</t>
         </is>
       </c>
-      <c r="Y72" t="inlineStr">
+      <c r="Z72" t="inlineStr">
         <is>
           <t>a35a84a5-de8a-4232-8e83-56571959cd5c</t>
         </is>
       </c>
-      <c r="Z72" t="inlineStr">
+      <c r="AA72" t="inlineStr">
         <is>
           <t>671ef239-098f-4d0b-bfd2-166912e226ae</t>
         </is>
@@ -6797,17 +6838,17 @@
           <t>Damage will be 28 if only the Thunder Godfist hits.</t>
         </is>
       </c>
-      <c r="X73" t="inlineStr">
+      <c r="Y73" t="inlineStr">
         <is>
           <t>ade9fdb2-ebe5-4010-9af6-22122fafbfa7</t>
         </is>
       </c>
-      <c r="Y73" t="inlineStr">
+      <c r="Z73" t="inlineStr">
         <is>
           <t>61aa2c38-48e3-4bb0-9132-9eb7abc72882</t>
         </is>
       </c>
-      <c r="Z73" t="inlineStr">
+      <c r="AA73" t="inlineStr">
         <is>
           <t>671ef239-098f-4d0b-bfd2-166912e226ae</t>
         </is>
@@ -6899,17 +6940,17 @@
           <t>BS</t>
         </is>
       </c>
-      <c r="X74" t="inlineStr">
+      <c r="Y74" t="inlineStr">
         <is>
           <t>8de90845-2c31-4181-81b1-494837824abb</t>
         </is>
       </c>
-      <c r="Y74" t="inlineStr">
+      <c r="Z74" t="inlineStr">
         <is>
           <t>4f091c07-e86b-4d56-a91f-029e8851a2bc</t>
         </is>
       </c>
-      <c r="Z74" t="inlineStr">
+      <c r="AA74" t="inlineStr">
         <is>
           <t>671ef239-098f-4d0b-bfd2-166912e226ae</t>
         </is>
@@ -6981,17 +7022,17 @@
           <t>LLm</t>
         </is>
       </c>
-      <c r="X75" t="inlineStr">
+      <c r="Y75" t="inlineStr">
         <is>
           <t>8438ef60-e448-466b-8dad-2a2f898d8254</t>
         </is>
       </c>
-      <c r="Y75" t="inlineStr">
+      <c r="Z75" t="inlineStr">
         <is>
           <t>d549dd8c-7b8f-47d8-9df2-a71108d1a511</t>
         </is>
       </c>
-      <c r="Z75" t="inlineStr">
+      <c r="AA75" t="inlineStr">
         <is>
           <t>8de90845-2c31-4181-81b1-494837824abb</t>
         </is>
@@ -7078,17 +7119,17 @@
           <t>LLmm</t>
         </is>
       </c>
-      <c r="X76" t="inlineStr">
+      <c r="Y76" t="inlineStr">
         <is>
           <t>839cd38f-c97a-4ee0-8ef4-8f5369ee0815</t>
         </is>
       </c>
-      <c r="Y76" t="inlineStr">
+      <c r="Z76" t="inlineStr">
         <is>
           <t>a8d4a430-cfbf-4ecf-8716-3c68d9c9fbac</t>
         </is>
       </c>
-      <c r="Z76" t="inlineStr">
+      <c r="AA76" t="inlineStr">
         <is>
           <t>8de90845-2c31-4181-81b1-494837824abb</t>
         </is>
@@ -7180,17 +7221,17 @@
           <t>Damage will be 28 if only the Thunder Godfist hits.</t>
         </is>
       </c>
-      <c r="X77" t="inlineStr">
+      <c r="Y77" t="inlineStr">
         <is>
           <t>614e83d4-fcab-4644-a466-f3820113dd9e</t>
         </is>
       </c>
-      <c r="Y77" t="inlineStr">
+      <c r="Z77" t="inlineStr">
         <is>
           <t>d769b421-5496-4981-a18a-f508ed792446</t>
         </is>
       </c>
-      <c r="Z77" t="inlineStr">
+      <c r="AA77" t="inlineStr">
         <is>
           <t>8de90845-2c31-4181-81b1-494837824abb</t>
         </is>
@@ -7282,17 +7323,17 @@
           <t>BS</t>
         </is>
       </c>
-      <c r="X78" t="inlineStr">
+      <c r="Y78" t="inlineStr">
         <is>
           <t>df5b5430-8e77-48f6-83b6-8d7561ded422</t>
         </is>
       </c>
-      <c r="Y78" t="inlineStr">
+      <c r="Z78" t="inlineStr">
         <is>
           <t>073f9e4c-be14-4c92-bb63-bf125f8be207</t>
         </is>
       </c>
-      <c r="Z78" t="inlineStr">
+      <c r="AA78" t="inlineStr">
         <is>
           <t>8de90845-2c31-4181-81b1-494837824abb</t>
         </is>
@@ -7364,17 +7405,17 @@
           <t>LLLm</t>
         </is>
       </c>
-      <c r="X79" t="inlineStr">
+      <c r="Y79" t="inlineStr">
         <is>
           <t>13aefd14-d087-4b03-9c70-7779fb41b891</t>
         </is>
       </c>
-      <c r="Y79" t="inlineStr">
+      <c r="Z79" t="inlineStr">
         <is>
           <t>5c2d120a-2126-472c-8377-cae6ec1949dc</t>
         </is>
       </c>
-      <c r="Z79" t="inlineStr">
+      <c r="AA79" t="inlineStr">
         <is>
           <t>df5b5430-8e77-48f6-83b6-8d7561ded422</t>
         </is>
@@ -7461,17 +7502,17 @@
           <t>LLLmm</t>
         </is>
       </c>
-      <c r="X80" t="inlineStr">
+      <c r="Y80" t="inlineStr">
         <is>
           <t>dd6b4fba-ebd7-46d9-822b-969ecfc3d134</t>
         </is>
       </c>
-      <c r="Y80" t="inlineStr">
+      <c r="Z80" t="inlineStr">
         <is>
           <t>1faab8f9-0b1a-438b-bc5e-321628c4aa0f</t>
         </is>
       </c>
-      <c r="Z80" t="inlineStr">
+      <c r="AA80" t="inlineStr">
         <is>
           <t>df5b5430-8e77-48f6-83b6-8d7561ded422</t>
         </is>
@@ -7563,17 +7604,17 @@
           <t>Damage will be 28 if only the Thunder Godfist hits.</t>
         </is>
       </c>
-      <c r="X81" t="inlineStr">
+      <c r="Y81" t="inlineStr">
         <is>
           <t>32f19890-efa9-4c4a-96cf-c6cfff6168fb</t>
         </is>
       </c>
-      <c r="Y81" t="inlineStr">
+      <c r="Z81" t="inlineStr">
         <is>
           <t>7a593df9-3ea4-4514-9ab1-28e69b85b8dc</t>
         </is>
       </c>
-      <c r="Z81" t="inlineStr">
+      <c r="AA81" t="inlineStr">
         <is>
           <t>df5b5430-8e77-48f6-83b6-8d7561ded422</t>
         </is>
@@ -7675,12 +7716,12 @@
           <t>Causes KS on a crouching opponent and SLD on CH.</t>
         </is>
       </c>
-      <c r="X82" t="inlineStr">
+      <c r="Y82" t="inlineStr">
         <is>
           <t>2b24052e-6ead-4141-9dcd-9212ec22ae08</t>
         </is>
       </c>
-      <c r="Y82" t="inlineStr">
+      <c r="Z82" t="inlineStr">
         <is>
           <t>2b22bff8-e297-419f-9687-2d3fd11bf342</t>
         </is>
@@ -7772,12 +7813,12 @@
           <t>When the Demon Scissors whiffs the opponent Heihachi receives5 points of damage.</t>
         </is>
       </c>
-      <c r="X83" t="inlineStr">
+      <c r="Y83" t="inlineStr">
         <is>
           <t>9379e996-1969-433c-9c6a-080c95b102f2</t>
         </is>
       </c>
-      <c r="Y83" t="inlineStr">
+      <c r="Z83" t="inlineStr">
         <is>
           <t>cd296010-10a3-4bf6-b145-36ae9dd91c58</t>
         </is>
@@ -7844,12 +7885,12 @@
           <t>Move can only be done when the opponent is knocked of his feet.</t>
         </is>
       </c>
-      <c r="X84" t="inlineStr">
+      <c r="Y84" t="inlineStr">
         <is>
           <t>94acdeb7-0477-4e1e-85c2-2db0d91ff8b0</t>
         </is>
       </c>
-      <c r="Y84" t="inlineStr">
+      <c r="Z84" t="inlineStr">
         <is>
           <t>b788230d-dc12-41e9-b8e9-1b3e7fe7f202</t>
         </is>
@@ -7901,12 +7942,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="X85" t="inlineStr">
+      <c r="Y85" t="inlineStr">
         <is>
           <t>dee0cf29-d794-47dd-ba10-3892d4998923</t>
         </is>
       </c>
-      <c r="Y85" t="inlineStr">
+      <c r="Z85" t="inlineStr">
         <is>
           <t>efba7a2e-fb22-4e3c-8840-2c08ce17fa6e</t>
         </is>
@@ -7958,12 +7999,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="X86" t="inlineStr">
+      <c r="Y86" t="inlineStr">
         <is>
           <t>a50232da-bfb3-4233-9a67-fedf01a87e85</t>
         </is>
       </c>
-      <c r="Y86" t="inlineStr">
+      <c r="Z86" t="inlineStr">
         <is>
           <t>4dcc8644-7a10-4584-a44c-ed10e3b62b44</t>
         </is>
@@ -8095,20 +8136,25 @@
       </c>
       <c r="X89" s="1" t="inlineStr">
         <is>
+          <t>Taggable</t>
+        </is>
+      </c>
+      <c r="Y89" s="1" t="inlineStr">
+        <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="Y89" s="1" t="inlineStr">
+      <c r="Z89" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="Z89" s="1" t="inlineStr">
+      <c r="AA89" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="AA89" s="1" t="inlineStr">
+      <c r="AB89" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
@@ -8195,12 +8241,12 @@
           <t>Heihachi will automaticly reverse any right kick attack during the Demon Tile Splitter animation.</t>
         </is>
       </c>
-      <c r="X90" t="inlineStr">
+      <c r="Y90" t="inlineStr">
         <is>
           <t>3ee1c731-c510-4ce8-abfe-895f352df4cf</t>
         </is>
       </c>
-      <c r="Y90" t="inlineStr">
+      <c r="Z90" t="inlineStr">
         <is>
           <t>37d96e68-85ef-4dc9-a8e4-fdec56988479</t>
         </is>
@@ -8332,20 +8378,25 @@
       </c>
       <c r="X93" s="1" t="inlineStr">
         <is>
+          <t>Taggable</t>
+        </is>
+      </c>
+      <c r="Y93" s="1" t="inlineStr">
+        <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="Y93" s="1" t="inlineStr">
+      <c r="Z93" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="Z93" s="1" t="inlineStr">
+      <c r="AA93" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="AA93" s="1" t="inlineStr">
+      <c r="AB93" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
@@ -8387,12 +8438,12 @@
           <t>mhhLLmhhmm</t>
         </is>
       </c>
-      <c r="Y94" t="inlineStr">
+      <c r="Z94" t="inlineStr">
         <is>
           <t>5e401bff-867a-4231-89fe-31140fb8cfa3</t>
         </is>
       </c>
-      <c r="AA94" t="inlineStr">
+      <c r="AB94" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -8434,12 +8485,12 @@
           <t>mhhLLmhhmm</t>
         </is>
       </c>
-      <c r="Y95" t="inlineStr">
+      <c r="Z95" t="inlineStr">
         <is>
           <t>4843994c-4a83-4e19-a59d-b3e33a4b6216</t>
         </is>
       </c>
-      <c r="AA95" t="inlineStr">
+      <c r="AB95" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -8481,12 +8532,12 @@
           <t>mhhLLmhmmm</t>
         </is>
       </c>
-      <c r="Y96" t="inlineStr">
+      <c r="Z96" t="inlineStr">
         <is>
           <t>b75ce8db-3ddd-40cc-b908-e15c334e3eff</t>
         </is>
       </c>
-      <c r="AA96" t="inlineStr">
+      <c r="AB96" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -8528,12 +8579,12 @@
           <t>hhhhmmlhmm</t>
         </is>
       </c>
-      <c r="Y97" t="inlineStr">
+      <c r="Z97" t="inlineStr">
         <is>
           <t>59b8bd40-2cec-44af-a5be-02b8f9c50b3c</t>
         </is>
       </c>
-      <c r="AA97" t="inlineStr">
+      <c r="AB97" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>

--- a/sources/heihachi_step7.xlsx
+++ b/sources/heihachi_step7.xlsx
@@ -425,7 +425,7 @@
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="26" customWidth="1" min="4" max="4"/>
     <col width="56" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
     <col width="7" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="11" customWidth="1" min="9" max="9"/>
@@ -3954,22 +3954,27 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>– ~1+2 [~u_~d]</t>
+          <t>– ~1+2</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>1&lt;2,2~1+2 [~u_~d]</t>
+          <t>1&lt;2,2~1+2</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>– Demon Executioner [SS]</t>
+          <t>– Demon Executioner</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Demon Slayer – Demon Executioner [SS]</t>
+          <t>Demon Slayer – Demon Executioner</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>(~u)SS; (~d)SS</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">

--- a/sources/heihachi_step7.xlsx
+++ b/sources/heihachi_step7.xlsx
@@ -933,6 +933,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>f46ce297-20aa-42e9-8fad-54b3f4704d3d</t>
+        </is>
+      </c>
       <c r="Z7" t="inlineStr">
         <is>
           <t>f46ce297-20aa-42e9-8fad-54b3f4704d3d</t>
@@ -995,6 +1000,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2bed6e68-3dcb-46ce-8b44-5a8ab9825180</t>
+        </is>
+      </c>
       <c r="Z8" t="inlineStr">
         <is>
           <t>2bed6e68-3dcb-46ce-8b44-5a8ab9825180</t>
@@ -1055,6 +1065,11 @@
       <c r="U9" t="inlineStr">
         <is>
           <t>None</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>94e89bd5-df08-4d1f-954d-ff55d170def7</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
@@ -8443,6 +8458,11 @@
           <t>mhhLLmhhmm</t>
         </is>
       </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>5e401bff-867a-4231-89fe-31140fb8cfa3</t>
+        </is>
+      </c>
       <c r="Z94" t="inlineStr">
         <is>
           <t>5e401bff-867a-4231-89fe-31140fb8cfa3</t>
@@ -8490,6 +8510,11 @@
           <t>mhhLLmhhmm</t>
         </is>
       </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>4843994c-4a83-4e19-a59d-b3e33a4b6216</t>
+        </is>
+      </c>
       <c r="Z95" t="inlineStr">
         <is>
           <t>4843994c-4a83-4e19-a59d-b3e33a4b6216</t>
@@ -8537,6 +8562,11 @@
           <t>mhhLLmhmmm</t>
         </is>
       </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>b75ce8db-3ddd-40cc-b908-e15c334e3eff</t>
+        </is>
+      </c>
       <c r="Z96" t="inlineStr">
         <is>
           <t>b75ce8db-3ddd-40cc-b908-e15c334e3eff</t>
@@ -8582,6 +8612,11 @@
       <c r="S97" t="inlineStr">
         <is>
           <t>hhhhmmlhmm</t>
+        </is>
+      </c>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>59b8bd40-2cec-44af-a5be-02b8f9c50b3c</t>
         </is>
       </c>
       <c r="Z97" t="inlineStr">

--- a/sources/heihachi_step7.xlsx
+++ b/sources/heihachi_step7.xlsx
@@ -417,37 +417,38 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB97"/>
+  <dimension ref="A1:AC97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
     <col width="25" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="56" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="7" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="11" customWidth="1" min="9" max="9"/>
-    <col width="20" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
-    <col width="16" customWidth="1" min="12" max="12"/>
-    <col width="17" customWidth="1" min="13" max="13"/>
-    <col width="22" customWidth="1" min="14" max="14"/>
-    <col width="24" customWidth="1" min="15" max="15"/>
-    <col width="12" customWidth="1" min="16" max="16"/>
-    <col width="24" customWidth="1" min="17" max="17"/>
-    <col width="12" customWidth="1" min="18" max="18"/>
-    <col width="16" customWidth="1" min="19" max="19"/>
-    <col width="12" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
-    <col width="13" customWidth="1" min="22" max="22"/>
-    <col width="200" customWidth="1" min="23" max="23"/>
-    <col width="10" customWidth="1" min="24" max="24"/>
-    <col width="38" customWidth="1" min="25" max="25"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="56" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="7" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
+    <col width="17" customWidth="1" min="14" max="14"/>
+    <col width="22" customWidth="1" min="15" max="15"/>
+    <col width="24" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="24" customWidth="1" min="18" max="18"/>
+    <col width="12" customWidth="1" min="19" max="19"/>
+    <col width="16" customWidth="1" min="20" max="20"/>
+    <col width="12" customWidth="1" min="21" max="21"/>
+    <col width="14" customWidth="1" min="22" max="22"/>
+    <col width="13" customWidth="1" min="23" max="23"/>
+    <col width="200" customWidth="1" min="24" max="24"/>
+    <col width="10" customWidth="1" min="25" max="25"/>
     <col width="38" customWidth="1" min="26" max="26"/>
     <col width="38" customWidth="1" min="27" max="27"/>
-    <col width="11" customWidth="1" min="28" max="28"/>
+    <col width="38" customWidth="1" min="28" max="28"/>
+    <col width="11" customWidth="1" min="29" max="29"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -475,125 +476,130 @@
       </c>
       <c r="D2" s="1" t="inlineStr">
         <is>
+          <t>Alt Commands Full</t>
+        </is>
+      </c>
+      <c r="E2" s="1" t="inlineStr">
+        <is>
           <t>Move Name</t>
         </is>
       </c>
-      <c r="E2" s="1" t="inlineStr">
+      <c r="F2" s="1" t="inlineStr">
         <is>
           <t>Move Name Full</t>
         </is>
       </c>
-      <c r="F2" s="1" t="inlineStr">
+      <c r="G2" s="1" t="inlineStr">
         <is>
           <t>To Stance</t>
         </is>
       </c>
-      <c r="G2" s="1" t="inlineStr">
+      <c r="H2" s="1" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
-      <c r="H2" s="1" t="inlineStr">
+      <c r="I2" s="1" t="inlineStr">
         <is>
           <t>Speed Full</t>
         </is>
       </c>
-      <c r="I2" s="1" t="inlineStr">
+      <c r="J2" s="1" t="inlineStr">
         <is>
           <t>Block Adv</t>
         </is>
       </c>
-      <c r="J2" s="1" t="inlineStr">
+      <c r="K2" s="1" t="inlineStr">
         <is>
           <t>Block Adv Full</t>
         </is>
       </c>
-      <c r="K2" s="1" t="inlineStr">
+      <c r="L2" s="1" t="inlineStr">
         <is>
           <t>Hit Adv</t>
         </is>
       </c>
-      <c r="L2" s="1" t="inlineStr">
+      <c r="M2" s="1" t="inlineStr">
         <is>
           <t>Hit Adv Full</t>
         </is>
       </c>
-      <c r="M2" s="1" t="inlineStr">
+      <c r="N2" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv</t>
         </is>
       </c>
-      <c r="N2" s="1" t="inlineStr">
+      <c r="O2" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv Full</t>
         </is>
       </c>
-      <c r="O2" s="1" t="inlineStr">
+      <c r="P2" s="1" t="inlineStr">
         <is>
           <t>Damage</t>
         </is>
       </c>
-      <c r="P2" s="1" t="inlineStr">
+      <c r="Q2" s="1" t="inlineStr">
         <is>
           <t>Damage Sum</t>
         </is>
       </c>
-      <c r="Q2" s="1" t="inlineStr">
+      <c r="R2" s="1" t="inlineStr">
         <is>
           <t>Damage Full</t>
         </is>
       </c>
-      <c r="R2" s="1" t="inlineStr">
+      <c r="S2" s="1" t="inlineStr">
         <is>
           <t>Hit Range</t>
         </is>
       </c>
-      <c r="S2" s="1" t="inlineStr">
+      <c r="T2" s="1" t="inlineStr">
         <is>
           <t>Hit Range Full</t>
         </is>
       </c>
-      <c r="T2" s="1" t="inlineStr">
+      <c r="U2" s="1" t="inlineStr">
         <is>
           <t>Throw Type</t>
         </is>
       </c>
-      <c r="U2" s="1" t="inlineStr">
+      <c r="V2" s="1" t="inlineStr">
         <is>
           <t>Throw Escape</t>
         </is>
       </c>
-      <c r="V2" s="1" t="inlineStr">
+      <c r="W2" s="1" t="inlineStr">
         <is>
           <t>Properties</t>
         </is>
       </c>
-      <c r="W2" s="1" t="inlineStr">
+      <c r="X2" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="X2" s="1" t="inlineStr">
+      <c r="Y2" s="1" t="inlineStr">
         <is>
           <t>Taggable</t>
         </is>
       </c>
-      <c r="Y2" s="1" t="inlineStr">
+      <c r="Z2" s="1" t="inlineStr">
         <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="Z2" s="1" t="inlineStr">
+      <c r="AA2" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="AA2" s="1" t="inlineStr">
+      <c r="AB2" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="AB2" s="1" t="inlineStr">
+      <c r="AC2" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
@@ -610,57 +616,57 @@
           <t>1+3</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>Neck Breaker</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>Neck Breaker</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>Front</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t>055edf24-00e6-4bb3-8ff4-9113ed584c70</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>6ad36a17-e53f-4652-ac7e-4de4d45e451e</t>
         </is>
@@ -677,57 +683,57 @@
           <t>2+4</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>Power Bomb</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>Power Bomb</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>Front</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
+      <c r="Z4" t="inlineStr">
         <is>
           <t>2a7efd25-998a-4518-b8b6-0ec6345106a4</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="AA4" t="inlineStr">
         <is>
           <t>522a334c-eb72-43e3-881e-74f4b50d8530</t>
         </is>
@@ -744,67 +750,67 @@
           <t>f,f+1+2</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>Stone Head</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>Stone Head</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>Front</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>1+2</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>Opponent can tech roll after the throw.; Special Tag Throw with Jun only. Jun finishes with a Reverse Arm Bar. Total damage is 30.</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
+      <c r="Z5" t="inlineStr">
         <is>
           <t>e115e974-d648-4855-89a2-19c755a06698</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
+      <c r="AA5" t="inlineStr">
         <is>
           <t>92ac3627-b2f3-45a8-8ce2-b2bfc7764f09</t>
         </is>
@@ -821,62 +827,62 @@
           <t>f,f+1+4</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>Head Butt Carnival</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>Head Butt Carnival</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>Front</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>1+2</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>Only against Jin, Heihachi, Lei, Kazuya, Jack-2, Gun Jack and Prototype Jack. They can reverse with 1 or 2. Heihachi can reverse again with 1+2, continuing back and forth. Damage is 42 against Kuma.</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
+      <c r="Z6" t="inlineStr">
         <is>
           <t>5fa5155a-0eba-4d3f-b813-a27edfe0bf4a</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
+      <c r="AA6" t="inlineStr">
         <is>
           <t>de8b4335-3cff-441f-aa66-9a78e87974b6</t>
         </is>
@@ -900,50 +906,55 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>2+4; 2+5</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>Tile Splitter Guillotine</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>Tile Splitter Guillotine</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>Left</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
+      <c r="Z7" t="inlineStr">
         <is>
           <t>f46ce297-20aa-42e9-8fad-54b3f4704d3d</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="AA7" t="inlineStr">
         <is>
           <t>f46ce297-20aa-42e9-8fad-54b3f4704d3d</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -967,50 +978,55 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>2+4; 2+5</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>Free Fall</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>Free Fall</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>46</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>46</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>46</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>Right</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>2bed6e68-3dcb-46ce-8b44-5a8ab9825180</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="AA8" t="inlineStr">
         <is>
           <t>2bed6e68-3dcb-46ce-8b44-5a8ab9825180</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -1034,50 +1050,55 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>2+4; 2+5</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>Atomic Drop</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>Atomic Drop</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>45</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>45</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>45</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>Back</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
+      <c r="Z9" t="inlineStr">
         <is>
           <t>94e89bd5-df08-4d1f-954d-ff55d170def7</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
+      <c r="AA9" t="inlineStr">
         <is>
           <t>94e89bd5-df08-4d1f-954d-ff55d170def7</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
+      <c r="AC9" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -1109,125 +1130,130 @@
       </c>
       <c r="D12" s="1" t="inlineStr">
         <is>
+          <t>Alt Commands Full</t>
+        </is>
+      </c>
+      <c r="E12" s="1" t="inlineStr">
+        <is>
           <t>Move Name</t>
         </is>
       </c>
-      <c r="E12" s="1" t="inlineStr">
+      <c r="F12" s="1" t="inlineStr">
         <is>
           <t>Move Name Full</t>
         </is>
       </c>
-      <c r="F12" s="1" t="inlineStr">
+      <c r="G12" s="1" t="inlineStr">
         <is>
           <t>To Stance</t>
         </is>
       </c>
-      <c r="G12" s="1" t="inlineStr">
+      <c r="H12" s="1" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
-      <c r="H12" s="1" t="inlineStr">
+      <c r="I12" s="1" t="inlineStr">
         <is>
           <t>Speed Full</t>
         </is>
       </c>
-      <c r="I12" s="1" t="inlineStr">
+      <c r="J12" s="1" t="inlineStr">
         <is>
           <t>Block Adv</t>
         </is>
       </c>
-      <c r="J12" s="1" t="inlineStr">
+      <c r="K12" s="1" t="inlineStr">
         <is>
           <t>Block Adv Full</t>
         </is>
       </c>
-      <c r="K12" s="1" t="inlineStr">
+      <c r="L12" s="1" t="inlineStr">
         <is>
           <t>Hit Adv</t>
         </is>
       </c>
-      <c r="L12" s="1" t="inlineStr">
+      <c r="M12" s="1" t="inlineStr">
         <is>
           <t>Hit Adv Full</t>
         </is>
       </c>
-      <c r="M12" s="1" t="inlineStr">
+      <c r="N12" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv</t>
         </is>
       </c>
-      <c r="N12" s="1" t="inlineStr">
+      <c r="O12" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv Full</t>
         </is>
       </c>
-      <c r="O12" s="1" t="inlineStr">
+      <c r="P12" s="1" t="inlineStr">
         <is>
           <t>Damage</t>
         </is>
       </c>
-      <c r="P12" s="1" t="inlineStr">
+      <c r="Q12" s="1" t="inlineStr">
         <is>
           <t>Damage Sum</t>
         </is>
       </c>
-      <c r="Q12" s="1" t="inlineStr">
+      <c r="R12" s="1" t="inlineStr">
         <is>
           <t>Damage Full</t>
         </is>
       </c>
-      <c r="R12" s="1" t="inlineStr">
+      <c r="S12" s="1" t="inlineStr">
         <is>
           <t>Hit Range</t>
         </is>
       </c>
-      <c r="S12" s="1" t="inlineStr">
+      <c r="T12" s="1" t="inlineStr">
         <is>
           <t>Hit Range Full</t>
         </is>
       </c>
-      <c r="T12" s="1" t="inlineStr">
+      <c r="U12" s="1" t="inlineStr">
         <is>
           <t>Throw Type</t>
         </is>
       </c>
-      <c r="U12" s="1" t="inlineStr">
+      <c r="V12" s="1" t="inlineStr">
         <is>
           <t>Throw Escape</t>
         </is>
       </c>
-      <c r="V12" s="1" t="inlineStr">
+      <c r="W12" s="1" t="inlineStr">
         <is>
           <t>Properties</t>
         </is>
       </c>
-      <c r="W12" s="1" t="inlineStr">
+      <c r="X12" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="X12" s="1" t="inlineStr">
+      <c r="Y12" s="1" t="inlineStr">
         <is>
           <t>Taggable</t>
         </is>
       </c>
-      <c r="Y12" s="1" t="inlineStr">
+      <c r="Z12" s="1" t="inlineStr">
         <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="Z12" s="1" t="inlineStr">
+      <c r="AA12" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="AA12" s="1" t="inlineStr">
+      <c r="AB12" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="AB12" s="1" t="inlineStr">
+      <c r="AC12" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
@@ -1244,77 +1270,77 @@
           <t>1</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>+1</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>+1</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="O13" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
+      <c r="P13" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr">
+      <c r="Q13" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr">
+      <c r="R13" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="Y13" t="inlineStr">
+      <c r="Z13" t="inlineStr">
         <is>
           <t>29f05378-4c42-41a0-a55f-5cc9bca80f34</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
+      <c r="AA13" t="inlineStr">
         <is>
           <t>a5a49b2d-da7e-44d1-9b17-38b7637f3a08</t>
         </is>
@@ -1331,77 +1357,77 @@
           <t>2</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
+      <c r="N14" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
+      <c r="O14" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr">
+      <c r="P14" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr">
+      <c r="Q14" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="Q14" t="inlineStr">
+      <c r="R14" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr">
+      <c r="S14" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
+      <c r="T14" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="Y14" t="inlineStr">
+      <c r="Z14" t="inlineStr">
         <is>
           <t>61030085-8620-468e-a73d-e20eff055cfd</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
+      <c r="AA14" t="inlineStr">
         <is>
           <t>ad1f150e-9eae-4e89-ac2b-5f5fa8a4b89e</t>
         </is>
@@ -1418,77 +1444,77 @@
           <t>3</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>-14</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>-14</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr">
+      <c r="N15" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
+      <c r="O15" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr">
+      <c r="P15" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr">
+      <c r="Q15" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="Q15" t="inlineStr">
+      <c r="R15" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="R15" t="inlineStr">
+      <c r="S15" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr">
+      <c r="T15" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="Y15" t="inlineStr">
+      <c r="Z15" t="inlineStr">
         <is>
           <t>ceaf0b9e-1026-4ae7-bba1-dce4c65e1b37</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
+      <c r="AA15" t="inlineStr">
         <is>
           <t>27e5cf01-5d6e-4d54-943e-97082c4f15a6</t>
         </is>
@@ -1505,31 +1531,26 @@
           <t>4</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t>-5</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>-5</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>KD</t>
@@ -1547,35 +1568,40 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="P16" t="inlineStr">
+      <c r="Q16" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="Q16" t="inlineStr">
+      <c r="R16" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="R16" t="inlineStr">
+      <c r="S16" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr">
+      <c r="T16" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="Y16" t="inlineStr">
+      <c r="Z16" t="inlineStr">
         <is>
           <t>f1d52cca-9dbb-4d7d-8b37-abe411e415a3</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
+      <c r="AA16" t="inlineStr">
         <is>
           <t>e171489f-567f-4d95-acb0-794681c07d75</t>
         </is>
@@ -1592,77 +1618,77 @@
           <t>f+1</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t>+3</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="K17" t="inlineStr">
         <is>
           <t>+3</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
+      <c r="L17" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr">
+      <c r="N17" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr">
+      <c r="O17" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr">
+      <c r="P17" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="P17" t="inlineStr">
+      <c r="Q17" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="Q17" t="inlineStr">
+      <c r="R17" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="R17" t="inlineStr">
+      <c r="S17" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr">
+      <c r="T17" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="Y17" t="inlineStr">
+      <c r="Z17" t="inlineStr">
         <is>
           <t>151a093a-4a24-4707-9fdc-85ae0ae9d089</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
+      <c r="AA17" t="inlineStr">
         <is>
           <t>5ee993a8-3ec1-4892-be2b-2d1dc4b43c29</t>
         </is>
@@ -1679,77 +1705,77 @@
           <t>f+2</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t>-13</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="K18" t="inlineStr">
         <is>
           <t>-13</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
+      <c r="L18" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr">
+      <c r="N18" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr">
+      <c r="O18" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr">
+      <c r="P18" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="P18" t="inlineStr">
+      <c r="Q18" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="Q18" t="inlineStr">
+      <c r="R18" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="R18" t="inlineStr">
+      <c r="S18" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr">
+      <c r="T18" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="Y18" t="inlineStr">
+      <c r="Z18" t="inlineStr">
         <is>
           <t>eb144a38-b7da-49ec-8e96-85c4769df844</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
+      <c r="AA18" t="inlineStr">
         <is>
           <t>a29ab714-ffc6-4f5c-9549-2b5d2984c5b1</t>
         </is>
@@ -1766,77 +1792,77 @@
           <t>f+3</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t>-14</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="K19" t="inlineStr">
         <is>
           <t>-14</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
+      <c r="L19" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
+      <c r="M19" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr">
+      <c r="N19" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr">
+      <c r="O19" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="O19" t="inlineStr">
+      <c r="P19" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="P19" t="inlineStr">
+      <c r="Q19" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="Q19" t="inlineStr">
+      <c r="R19" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="R19" t="inlineStr">
+      <c r="S19" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr">
+      <c r="T19" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="Y19" t="inlineStr">
+      <c r="Z19" t="inlineStr">
         <is>
           <t>b885f59d-33f7-4aa4-b758-c5d018dbbefa</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
+      <c r="AA19" t="inlineStr">
         <is>
           <t>b09b5581-7097-4941-a01f-0eabfd91442f</t>
         </is>
@@ -1853,31 +1879,26 @@
           <t>f+4</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="J20" t="inlineStr">
         <is>
           <t>-5</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
+      <c r="K20" t="inlineStr">
         <is>
           <t>-5</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>KD</t>
@@ -1895,35 +1916,40 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="P20" t="inlineStr">
+      <c r="Q20" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="Q20" t="inlineStr">
+      <c r="R20" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="R20" t="inlineStr">
+      <c r="S20" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr">
+      <c r="T20" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="Y20" t="inlineStr">
+      <c r="Z20" t="inlineStr">
         <is>
           <t>8662a3d8-6f93-4295-bbbe-b15e2ce515b5</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
+      <c r="AA20" t="inlineStr">
         <is>
           <t>f23dc020-3cbc-46ec-9ff6-9f6942d0b908</t>
         </is>
@@ -1940,77 +1966,77 @@
           <t>d+1</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t>-8</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
+      <c r="K21" t="inlineStr">
         <is>
           <t>-8</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
+      <c r="L21" t="inlineStr">
         <is>
           <t>-8</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr">
+      <c r="M21" t="inlineStr">
         <is>
           <t>-8</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr">
+      <c r="N21" t="inlineStr">
         <is>
           <t>+4</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr">
+      <c r="O21" t="inlineStr">
         <is>
           <t>+4</t>
         </is>
       </c>
-      <c r="O21" t="inlineStr">
+      <c r="P21" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="P21" t="inlineStr">
+      <c r="Q21" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q21" t="inlineStr">
+      <c r="R21" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="R21" t="inlineStr">
+      <c r="S21" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr">
+      <c r="T21" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="Y21" t="inlineStr">
+      <c r="Z21" t="inlineStr">
         <is>
           <t>30df2932-071a-443e-b19f-649d3a9c0960</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
+      <c r="AA21" t="inlineStr">
         <is>
           <t>87d16cd4-ad18-401f-96d2-f66948f7f066</t>
         </is>
@@ -2027,77 +2053,77 @@
           <t>d+2</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
+      <c r="K22" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
+      <c r="L22" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr">
+      <c r="M22" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr">
+      <c r="N22" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr">
+      <c r="O22" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="O22" t="inlineStr">
+      <c r="P22" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="P22" t="inlineStr">
+      <c r="Q22" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="Q22" t="inlineStr">
+      <c r="R22" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="R22" t="inlineStr">
+      <c r="S22" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="S22" t="inlineStr">
+      <c r="T22" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="Y22" t="inlineStr">
+      <c r="Z22" t="inlineStr">
         <is>
           <t>4911413b-5c5a-46d9-969b-975b22762247</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
+      <c r="AA22" t="inlineStr">
         <is>
           <t>bd7b7be9-b98f-4a2f-a697-9726f37d7f29</t>
         </is>
@@ -2114,77 +2140,77 @@
           <t>d+3</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="H23" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="I23" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
+      <c r="J23" t="inlineStr">
         <is>
           <t>-17</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
+      <c r="K23" t="inlineStr">
         <is>
           <t>-17</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
+      <c r="L23" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
+      <c r="M23" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr">
+      <c r="N23" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr">
+      <c r="O23" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="O23" t="inlineStr">
+      <c r="P23" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="P23" t="inlineStr">
+      <c r="Q23" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="Q23" t="inlineStr">
+      <c r="R23" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="R23" t="inlineStr">
+      <c r="S23" t="inlineStr">
         <is>
           <t>l</t>
         </is>
       </c>
-      <c r="S23" t="inlineStr">
+      <c r="T23" t="inlineStr">
         <is>
           <t>l</t>
         </is>
       </c>
-      <c r="Y23" t="inlineStr">
+      <c r="Z23" t="inlineStr">
         <is>
           <t>c833b466-b036-4bac-a0b6-71c87f3b2e5d</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
+      <c r="AA23" t="inlineStr">
         <is>
           <t>751d7427-8654-498e-b79d-bc0d285469f4</t>
         </is>
@@ -2201,77 +2227,77 @@
           <t>d+4</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="H24" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="I24" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
+      <c r="J24" t="inlineStr">
         <is>
           <t>-8</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr">
+      <c r="K24" t="inlineStr">
         <is>
           <t>-8</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
+      <c r="L24" t="inlineStr">
         <is>
           <t>+3</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr">
+      <c r="M24" t="inlineStr">
         <is>
           <t>+3</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr">
+      <c r="N24" t="inlineStr">
         <is>
           <t>+3</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr">
+      <c r="O24" t="inlineStr">
         <is>
           <t>+3</t>
         </is>
       </c>
-      <c r="O24" t="inlineStr">
+      <c r="P24" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="P24" t="inlineStr">
+      <c r="Q24" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="Q24" t="inlineStr">
+      <c r="R24" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="R24" t="inlineStr">
+      <c r="S24" t="inlineStr">
         <is>
           <t>l</t>
         </is>
       </c>
-      <c r="S24" t="inlineStr">
+      <c r="T24" t="inlineStr">
         <is>
           <t>l</t>
         </is>
       </c>
-      <c r="Y24" t="inlineStr">
+      <c r="Z24" t="inlineStr">
         <is>
           <t>5e8a47cc-f2d6-4273-8a70-4329b9604c1e</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
+      <c r="AA24" t="inlineStr">
         <is>
           <t>f649446d-5c13-4cb1-892b-9e55345cca38</t>
         </is>
@@ -2288,77 +2314,77 @@
           <t>FC+1</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="H25" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
+      <c r="K25" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
+      <c r="L25" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr">
+      <c r="M25" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="M25" t="inlineStr">
+      <c r="N25" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr">
+      <c r="O25" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="O25" t="inlineStr">
+      <c r="P25" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="P25" t="inlineStr">
+      <c r="Q25" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="Q25" t="inlineStr">
+      <c r="R25" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="R25" t="inlineStr">
+      <c r="S25" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="S25" t="inlineStr">
+      <c r="T25" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="Y25" t="inlineStr">
+      <c r="Z25" t="inlineStr">
         <is>
           <t>9900670c-8afe-4c73-a313-1cb75c1bce79</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
+      <c r="AA25" t="inlineStr">
         <is>
           <t>fae825e3-99c8-440a-955e-2a814ff27735</t>
         </is>
@@ -2375,77 +2401,77 @@
           <t>FC+2</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="H26" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="I26" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
+      <c r="J26" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr">
+      <c r="K26" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
+      <c r="L26" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr">
+      <c r="M26" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr">
+      <c r="N26" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr">
+      <c r="O26" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="O26" t="inlineStr">
+      <c r="P26" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="P26" t="inlineStr">
+      <c r="Q26" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="Q26" t="inlineStr">
+      <c r="R26" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="R26" t="inlineStr">
+      <c r="S26" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="S26" t="inlineStr">
+      <c r="T26" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="Y26" t="inlineStr">
+      <c r="Z26" t="inlineStr">
         <is>
           <t>90023022-398a-4423-833a-ba875bdfe248</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
+      <c r="AA26" t="inlineStr">
         <is>
           <t>5f9c0cb6-4f0f-443b-9d4b-2d9dc2782022</t>
         </is>
@@ -2462,77 +2488,77 @@
           <t>FC+3</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="H27" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="I27" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
+      <c r="J27" t="inlineStr">
         <is>
           <t>-9</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
+      <c r="K27" t="inlineStr">
         <is>
           <t>-9</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
+      <c r="L27" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr">
+      <c r="M27" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr">
+      <c r="N27" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr">
+      <c r="O27" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="O27" t="inlineStr">
+      <c r="P27" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="P27" t="inlineStr">
+      <c r="Q27" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="Q27" t="inlineStr">
+      <c r="R27" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="R27" t="inlineStr">
+      <c r="S27" t="inlineStr">
         <is>
           <t>l</t>
         </is>
       </c>
-      <c r="S27" t="inlineStr">
+      <c r="T27" t="inlineStr">
         <is>
           <t>l</t>
         </is>
       </c>
-      <c r="Y27" t="inlineStr">
+      <c r="Z27" t="inlineStr">
         <is>
           <t>053a1ac4-73a0-4cb9-8dac-87ff3bc99058</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
+      <c r="AA27" t="inlineStr">
         <is>
           <t>3498e460-1be1-4a5f-8714-abecbeefce3b</t>
         </is>
@@ -2549,77 +2575,77 @@
           <t>FC+4</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="H28" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="I28" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
+      <c r="J28" t="inlineStr">
         <is>
           <t>-9</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr">
+      <c r="K28" t="inlineStr">
         <is>
           <t>-9</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
+      <c r="L28" t="inlineStr">
         <is>
           <t>+3</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr">
+      <c r="M28" t="inlineStr">
         <is>
           <t>+3</t>
         </is>
       </c>
-      <c r="M28" t="inlineStr">
+      <c r="N28" t="inlineStr">
         <is>
           <t>+3</t>
         </is>
       </c>
-      <c r="N28" t="inlineStr">
+      <c r="O28" t="inlineStr">
         <is>
           <t>+3</t>
         </is>
       </c>
-      <c r="O28" t="inlineStr">
+      <c r="P28" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="P28" t="inlineStr">
+      <c r="Q28" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="Q28" t="inlineStr">
+      <c r="R28" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="R28" t="inlineStr">
+      <c r="S28" t="inlineStr">
         <is>
           <t>l</t>
         </is>
       </c>
-      <c r="S28" t="inlineStr">
+      <c r="T28" t="inlineStr">
         <is>
           <t>l</t>
         </is>
       </c>
-      <c r="Y28" t="inlineStr">
+      <c r="Z28" t="inlineStr">
         <is>
           <t>3961163a-e7d3-4791-a056-23f7b4a65ce1</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
+      <c r="AA28" t="inlineStr">
         <is>
           <t>e73d65a4-ac30-47c9-962e-2a9034080fa4</t>
         </is>
@@ -2636,77 +2662,77 @@
           <t>WS+1</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="H29" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="I29" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
+      <c r="J29" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr">
+      <c r="K29" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
+      <c r="L29" t="inlineStr">
         <is>
           <t>+8</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr">
+      <c r="M29" t="inlineStr">
         <is>
           <t>+8</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr">
+      <c r="N29" t="inlineStr">
         <is>
           <t>+8</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr">
+      <c r="O29" t="inlineStr">
         <is>
           <t>+8</t>
         </is>
       </c>
-      <c r="O29" t="inlineStr">
+      <c r="P29" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="P29" t="inlineStr">
+      <c r="Q29" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="Q29" t="inlineStr">
+      <c r="R29" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="R29" t="inlineStr">
+      <c r="S29" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="S29" t="inlineStr">
+      <c r="T29" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="Y29" t="inlineStr">
+      <c r="Z29" t="inlineStr">
         <is>
           <t>ff808c39-0942-4f29-9af2-0c1d8937368c</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
+      <c r="AA29" t="inlineStr">
         <is>
           <t>a2218298-0d90-488a-ba7e-1c61827a703e</t>
         </is>
@@ -2723,41 +2749,36 @@
           <t>WS+2</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="H30" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="I30" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
+      <c r="J30" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr">
+      <c r="K30" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
+      <c r="L30" t="inlineStr">
         <is>
           <t>+4</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr">
+      <c r="M30" t="inlineStr">
         <is>
           <t>+4</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
       <c r="N30" t="inlineStr">
         <is>
           <t>KD</t>
@@ -2765,35 +2786,40 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="P30" t="inlineStr">
+      <c r="Q30" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="Q30" t="inlineStr">
+      <c r="R30" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="R30" t="inlineStr">
+      <c r="S30" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="S30" t="inlineStr">
+      <c r="T30" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="Y30" t="inlineStr">
+      <c r="Z30" t="inlineStr">
         <is>
           <t>732d91c7-ae81-435c-ba3e-709873e67d97</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
+      <c r="AA30" t="inlineStr">
         <is>
           <t>f6367452-5e87-464f-9b47-d20b42453746</t>
         </is>
@@ -2810,31 +2836,26 @@
           <t>WS+3</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="H31" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="I31" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
+      <c r="J31" t="inlineStr">
         <is>
           <t>-16</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr">
+      <c r="K31" t="inlineStr">
         <is>
           <t>-16</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>KD</t>
@@ -2852,35 +2873,40 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="P31" t="inlineStr">
+      <c r="Q31" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="Q31" t="inlineStr">
+      <c r="R31" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="R31" t="inlineStr">
+      <c r="S31" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="S31" t="inlineStr">
+      <c r="T31" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="Y31" t="inlineStr">
+      <c r="Z31" t="inlineStr">
         <is>
           <t>317dcdb4-06ab-4843-b04c-6f6653f87ad9</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
+      <c r="AA31" t="inlineStr">
         <is>
           <t>3884d910-0287-4c6d-ac21-d5039a604305</t>
         </is>
@@ -2897,77 +2923,77 @@
           <t>WS+4</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="H32" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
+      <c r="I32" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
+      <c r="J32" t="inlineStr">
         <is>
           <t>-5</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr">
+      <c r="K32" t="inlineStr">
         <is>
           <t>-5</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr">
+      <c r="L32" t="inlineStr">
         <is>
           <t>+6</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr">
+      <c r="M32" t="inlineStr">
         <is>
           <t>+6</t>
         </is>
       </c>
-      <c r="M32" t="inlineStr">
+      <c r="N32" t="inlineStr">
         <is>
           <t>+6</t>
         </is>
       </c>
-      <c r="N32" t="inlineStr">
+      <c r="O32" t="inlineStr">
         <is>
           <t>+6</t>
         </is>
       </c>
-      <c r="O32" t="inlineStr">
+      <c r="P32" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="P32" t="inlineStr">
+      <c r="Q32" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="Q32" t="inlineStr">
+      <c r="R32" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="R32" t="inlineStr">
+      <c r="S32" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="S32" t="inlineStr">
+      <c r="T32" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="Y32" t="inlineStr">
+      <c r="Z32" t="inlineStr">
         <is>
           <t>996d2223-e5ac-4917-ac11-bdda927a8fa9</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
+      <c r="AA32" t="inlineStr">
         <is>
           <t>494df9c0-dd89-4489-a417-6d6480d86ea5</t>
         </is>
@@ -2984,77 +3010,77 @@
           <t>df+1</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="H33" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
+      <c r="I33" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
+      <c r="J33" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr">
+      <c r="K33" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr">
+      <c r="L33" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr">
+      <c r="M33" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="M33" t="inlineStr">
+      <c r="N33" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="N33" t="inlineStr">
+      <c r="O33" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="O33" t="inlineStr">
+      <c r="P33" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="P33" t="inlineStr">
+      <c r="Q33" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="Q33" t="inlineStr">
+      <c r="R33" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="R33" t="inlineStr">
+      <c r="S33" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="S33" t="inlineStr">
+      <c r="T33" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="Y33" t="inlineStr">
+      <c r="Z33" t="inlineStr">
         <is>
           <t>532a8f4f-8179-47ad-8f5e-cd79cbcb2d38</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
+      <c r="AA33" t="inlineStr">
         <is>
           <t>f07eb2c7-fa12-4dbe-bab0-c9f9b5a75c14</t>
         </is>
@@ -3071,77 +3097,77 @@
           <t>df+2</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="H34" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
+      <c r="I34" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
+      <c r="J34" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr">
+      <c r="K34" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr">
+      <c r="L34" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr">
+      <c r="M34" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="M34" t="inlineStr">
+      <c r="N34" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="N34" t="inlineStr">
+      <c r="O34" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="O34" t="inlineStr">
+      <c r="P34" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="P34" t="inlineStr">
+      <c r="Q34" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="Q34" t="inlineStr">
+      <c r="R34" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="R34" t="inlineStr">
+      <c r="S34" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="S34" t="inlineStr">
+      <c r="T34" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="Y34" t="inlineStr">
+      <c r="Z34" t="inlineStr">
         <is>
           <t>03e7a494-42af-4c02-ae04-fe6e3d544130</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
+      <c r="AA34" t="inlineStr">
         <is>
           <t>4bb45d34-7291-4b69-bd2f-a93895a01886</t>
         </is>
@@ -3158,77 +3184,77 @@
           <t>df+3</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="H35" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
+      <c r="I35" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
+      <c r="J35" t="inlineStr">
         <is>
           <t>-9</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr">
+      <c r="K35" t="inlineStr">
         <is>
           <t>-9</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr">
+      <c r="L35" t="inlineStr">
         <is>
           <t>+2</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr">
+      <c r="M35" t="inlineStr">
         <is>
           <t>+2</t>
         </is>
       </c>
-      <c r="M35" t="inlineStr">
+      <c r="N35" t="inlineStr">
         <is>
           <t>+2</t>
         </is>
       </c>
-      <c r="N35" t="inlineStr">
+      <c r="O35" t="inlineStr">
         <is>
           <t>+2</t>
         </is>
       </c>
-      <c r="O35" t="inlineStr">
+      <c r="P35" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="P35" t="inlineStr">
+      <c r="Q35" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="Q35" t="inlineStr">
+      <c r="R35" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="R35" t="inlineStr">
+      <c r="S35" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="S35" t="inlineStr">
+      <c r="T35" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="Y35" t="inlineStr">
+      <c r="Z35" t="inlineStr">
         <is>
           <t>b6b2bbe2-54ac-4521-8e16-8e4164acccfb</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
+      <c r="AA35" t="inlineStr">
         <is>
           <t>d6106ca6-1e22-46b5-aa2c-c273dcfd0c04</t>
         </is>
@@ -3245,77 +3271,77 @@
           <t>df+4</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
+      <c r="H36" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
+      <c r="I36" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
+      <c r="J36" t="inlineStr">
         <is>
           <t>-4</t>
         </is>
       </c>
-      <c r="J36" t="inlineStr">
+      <c r="K36" t="inlineStr">
         <is>
           <t>-4</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr">
+      <c r="L36" t="inlineStr">
         <is>
           <t>+7</t>
         </is>
       </c>
-      <c r="L36" t="inlineStr">
+      <c r="M36" t="inlineStr">
         <is>
           <t>+7</t>
         </is>
       </c>
-      <c r="M36" t="inlineStr">
+      <c r="N36" t="inlineStr">
         <is>
           <t>+7</t>
         </is>
       </c>
-      <c r="N36" t="inlineStr">
+      <c r="O36" t="inlineStr">
         <is>
           <t>+7</t>
         </is>
       </c>
-      <c r="O36" t="inlineStr">
+      <c r="P36" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="P36" t="inlineStr">
+      <c r="Q36" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q36" t="inlineStr">
+      <c r="R36" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="R36" t="inlineStr">
+      <c r="S36" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="S36" t="inlineStr">
+      <c r="T36" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="Y36" t="inlineStr">
+      <c r="Z36" t="inlineStr">
         <is>
           <t>c02d47de-47e8-4faa-9ada-5b2889324555</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
+      <c r="AA36" t="inlineStr">
         <is>
           <t>bf5265d6-4a33-4218-b469-1af5406c7075</t>
         </is>
@@ -3347,125 +3373,130 @@
       </c>
       <c r="D39" s="1" t="inlineStr">
         <is>
+          <t>Alt Commands Full</t>
+        </is>
+      </c>
+      <c r="E39" s="1" t="inlineStr">
+        <is>
           <t>Move Name</t>
         </is>
       </c>
-      <c r="E39" s="1" t="inlineStr">
+      <c r="F39" s="1" t="inlineStr">
         <is>
           <t>Move Name Full</t>
         </is>
       </c>
-      <c r="F39" s="1" t="inlineStr">
+      <c r="G39" s="1" t="inlineStr">
         <is>
           <t>To Stance</t>
         </is>
       </c>
-      <c r="G39" s="1" t="inlineStr">
+      <c r="H39" s="1" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
-      <c r="H39" s="1" t="inlineStr">
+      <c r="I39" s="1" t="inlineStr">
         <is>
           <t>Speed Full</t>
         </is>
       </c>
-      <c r="I39" s="1" t="inlineStr">
+      <c r="J39" s="1" t="inlineStr">
         <is>
           <t>Block Adv</t>
         </is>
       </c>
-      <c r="J39" s="1" t="inlineStr">
+      <c r="K39" s="1" t="inlineStr">
         <is>
           <t>Block Adv Full</t>
         </is>
       </c>
-      <c r="K39" s="1" t="inlineStr">
+      <c r="L39" s="1" t="inlineStr">
         <is>
           <t>Hit Adv</t>
         </is>
       </c>
-      <c r="L39" s="1" t="inlineStr">
+      <c r="M39" s="1" t="inlineStr">
         <is>
           <t>Hit Adv Full</t>
         </is>
       </c>
-      <c r="M39" s="1" t="inlineStr">
+      <c r="N39" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv</t>
         </is>
       </c>
-      <c r="N39" s="1" t="inlineStr">
+      <c r="O39" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv Full</t>
         </is>
       </c>
-      <c r="O39" s="1" t="inlineStr">
+      <c r="P39" s="1" t="inlineStr">
         <is>
           <t>Damage</t>
         </is>
       </c>
-      <c r="P39" s="1" t="inlineStr">
+      <c r="Q39" s="1" t="inlineStr">
         <is>
           <t>Damage Sum</t>
         </is>
       </c>
-      <c r="Q39" s="1" t="inlineStr">
+      <c r="R39" s="1" t="inlineStr">
         <is>
           <t>Damage Full</t>
         </is>
       </c>
-      <c r="R39" s="1" t="inlineStr">
+      <c r="S39" s="1" t="inlineStr">
         <is>
           <t>Hit Range</t>
         </is>
       </c>
-      <c r="S39" s="1" t="inlineStr">
+      <c r="T39" s="1" t="inlineStr">
         <is>
           <t>Hit Range Full</t>
         </is>
       </c>
-      <c r="T39" s="1" t="inlineStr">
+      <c r="U39" s="1" t="inlineStr">
         <is>
           <t>Throw Type</t>
         </is>
       </c>
-      <c r="U39" s="1" t="inlineStr">
+      <c r="V39" s="1" t="inlineStr">
         <is>
           <t>Throw Escape</t>
         </is>
       </c>
-      <c r="V39" s="1" t="inlineStr">
+      <c r="W39" s="1" t="inlineStr">
         <is>
           <t>Properties</t>
         </is>
       </c>
-      <c r="W39" s="1" t="inlineStr">
+      <c r="X39" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="X39" s="1" t="inlineStr">
+      <c r="Y39" s="1" t="inlineStr">
         <is>
           <t>Taggable</t>
         </is>
       </c>
-      <c r="Y39" s="1" t="inlineStr">
+      <c r="Z39" s="1" t="inlineStr">
         <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="Z39" s="1" t="inlineStr">
+      <c r="AA39" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="AA39" s="1" t="inlineStr">
+      <c r="AB39" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="AB39" s="1" t="inlineStr">
+      <c r="AC39" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
@@ -3482,92 +3513,92 @@
           <t>b+1</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
+      <c r="E40" t="inlineStr">
         <is>
           <t>Alter Splitter</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="F40" t="inlineStr">
         <is>
           <t>Alter Splitter</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
+      <c r="H40" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
+      <c r="I40" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
+      <c r="J40" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="J40" t="inlineStr">
+      <c r="K40" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr">
+      <c r="L40" t="inlineStr">
         <is>
           <t>+3</t>
         </is>
       </c>
-      <c r="L40" t="inlineStr">
+      <c r="M40" t="inlineStr">
         <is>
           <t>+3</t>
         </is>
       </c>
-      <c r="M40" t="inlineStr">
+      <c r="N40" t="inlineStr">
         <is>
           <t>+15</t>
         </is>
       </c>
-      <c r="N40" t="inlineStr">
+      <c r="O40" t="inlineStr">
         <is>
           <t>+15</t>
         </is>
       </c>
-      <c r="O40" t="inlineStr">
+      <c r="P40" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="P40" t="inlineStr">
+      <c r="Q40" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="Q40" t="inlineStr">
+      <c r="R40" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="R40" t="inlineStr">
+      <c r="S40" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="S40" t="inlineStr">
+      <c r="T40" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="V40" t="inlineStr">
+      <c r="W40" t="inlineStr">
         <is>
           <t>KSc KSco GB</t>
         </is>
       </c>
-      <c r="Y40" t="inlineStr">
+      <c r="Z40" t="inlineStr">
         <is>
           <t>ae5886ed-653a-48be-b9c7-15ef4aacda57</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
+      <c r="AA40" t="inlineStr">
         <is>
           <t>273d9ede-8672-4cea-8b4a-9b17f83ef955</t>
         </is>
@@ -3584,87 +3615,87 @@
           <t>1&lt;2</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="E41" t="inlineStr">
         <is>
           <t>Double Punch</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="F41" t="inlineStr">
         <is>
           <t>Double Punch</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
+      <c r="H41" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
+      <c r="I41" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
+      <c r="J41" t="inlineStr">
         <is>
           <t>+1 0</t>
         </is>
       </c>
-      <c r="J41" t="inlineStr">
+      <c r="K41" t="inlineStr">
         <is>
           <t>+1 0</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr">
+      <c r="L41" t="inlineStr">
         <is>
           <t>+9 +8</t>
         </is>
       </c>
-      <c r="L41" t="inlineStr">
+      <c r="M41" t="inlineStr">
         <is>
           <t>+9 +8</t>
         </is>
       </c>
-      <c r="M41" t="inlineStr">
+      <c r="N41" t="inlineStr">
         <is>
           <t>+9 +8</t>
         </is>
       </c>
-      <c r="N41" t="inlineStr">
+      <c r="O41" t="inlineStr">
         <is>
           <t>+9 +8</t>
         </is>
       </c>
-      <c r="O41" t="inlineStr">
+      <c r="P41" t="inlineStr">
         <is>
           <t>5,8</t>
         </is>
       </c>
-      <c r="P41" t="inlineStr">
+      <c r="Q41" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="Q41" t="inlineStr">
+      <c r="R41" t="inlineStr">
         <is>
           <t>5,8</t>
         </is>
       </c>
-      <c r="R41" t="inlineStr">
+      <c r="S41" t="inlineStr">
         <is>
           <t>hh</t>
         </is>
       </c>
-      <c r="S41" t="inlineStr">
+      <c r="T41" t="inlineStr">
         <is>
           <t>hh</t>
         </is>
       </c>
-      <c r="Y41" t="inlineStr">
+      <c r="Z41" t="inlineStr">
         <is>
           <t>c28a50b0-4d64-4d99-af29-2092c90c0512</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
+      <c r="AA41" t="inlineStr">
         <is>
           <t>c1cf7b8f-c486-4fef-96b7-5a636bbc6b41</t>
         </is>
@@ -3681,92 +3712,92 @@
           <t>1&lt;2,4</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
+      <c r="E42" t="inlineStr">
         <is>
           <t>– Roundhouse</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="F42" t="inlineStr">
         <is>
           <t>Double Punch – Roundhouse</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
+      <c r="I42" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
+      <c r="J42" t="inlineStr">
         <is>
           <t>-19</t>
         </is>
       </c>
-      <c r="J42" t="inlineStr">
+      <c r="K42" t="inlineStr">
         <is>
           <t>+1 0 -19</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
       <c r="L42" t="inlineStr">
         <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
           <t>+9 +8 KD</t>
         </is>
       </c>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
       <c r="N42" t="inlineStr">
         <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
           <t>+9 +8 KD</t>
         </is>
       </c>
-      <c r="O42" t="inlineStr">
+      <c r="P42" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="P42" t="inlineStr">
+      <c r="Q42" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q42" t="inlineStr">
+      <c r="R42" t="inlineStr">
         <is>
           <t>5,8,15</t>
         </is>
       </c>
-      <c r="R42" t="inlineStr">
+      <c r="S42" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="S42" t="inlineStr">
+      <c r="T42" t="inlineStr">
         <is>
           <t>hhh</t>
         </is>
       </c>
-      <c r="V42" t="inlineStr">
+      <c r="W42" t="inlineStr">
         <is>
           <t>CSc</t>
         </is>
       </c>
-      <c r="Y42" t="inlineStr">
+      <c r="Z42" t="inlineStr">
         <is>
           <t>ce7b2f27-c16a-4507-b110-dd9638bb5ade</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
+      <c r="AA42" t="inlineStr">
         <is>
           <t>d5ead6e5-b493-4f13-a54e-e9a86228b0a1</t>
         </is>
       </c>
-      <c r="AA42" t="inlineStr">
+      <c r="AB42" t="inlineStr">
         <is>
           <t>c28a50b0-4d64-4d99-af29-2092c90c0512</t>
         </is>
@@ -3783,87 +3814,87 @@
           <t>1,1&lt;2</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
+      <c r="E43" t="inlineStr">
         <is>
           <t>Shining Fists</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
+      <c r="F43" t="inlineStr">
         <is>
           <t>Shining Fists</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
+      <c r="H43" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
+      <c r="I43" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
+      <c r="J43" t="inlineStr">
         <is>
           <t>+1 +1 -17</t>
         </is>
       </c>
-      <c r="J43" t="inlineStr">
+      <c r="K43" t="inlineStr">
         <is>
           <t>+1 +1 -17</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr">
+      <c r="L43" t="inlineStr">
         <is>
           <t>+9 +9 KD</t>
         </is>
       </c>
-      <c r="L43" t="inlineStr">
+      <c r="M43" t="inlineStr">
         <is>
           <t>+9 +9 KD</t>
         </is>
       </c>
-      <c r="M43" t="inlineStr">
+      <c r="N43" t="inlineStr">
         <is>
           <t>+9 +9 KD</t>
         </is>
       </c>
-      <c r="N43" t="inlineStr">
+      <c r="O43" t="inlineStr">
         <is>
           <t>+9 +9 KD</t>
         </is>
       </c>
-      <c r="O43" t="inlineStr">
+      <c r="P43" t="inlineStr">
         <is>
           <t>5,8,18</t>
         </is>
       </c>
-      <c r="P43" t="inlineStr">
+      <c r="Q43" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="Q43" t="inlineStr">
+      <c r="R43" t="inlineStr">
         <is>
           <t>5,8,18</t>
         </is>
       </c>
-      <c r="R43" t="inlineStr">
+      <c r="S43" t="inlineStr">
         <is>
           <t>hhm</t>
         </is>
       </c>
-      <c r="S43" t="inlineStr">
+      <c r="T43" t="inlineStr">
         <is>
           <t>hhm</t>
         </is>
       </c>
-      <c r="Y43" t="inlineStr">
+      <c r="Z43" t="inlineStr">
         <is>
           <t>5a1a5efc-057d-4db1-97bf-1013a5f7eb7d</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
+      <c r="AA43" t="inlineStr">
         <is>
           <t>4c02bf2e-9cdb-4b12-813c-2e5cad3aa246</t>
         </is>
@@ -3880,87 +3911,87 @@
           <t>1&lt;2,2</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
+      <c r="E44" t="inlineStr">
         <is>
           <t>Demon Slayer</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="F44" t="inlineStr">
         <is>
           <t>Demon Slayer</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
+      <c r="H44" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
+      <c r="I44" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
+      <c r="J44" t="inlineStr">
         <is>
           <t>+1 0 -12</t>
         </is>
       </c>
-      <c r="J44" t="inlineStr">
+      <c r="K44" t="inlineStr">
         <is>
           <t>+1 0 -12</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr">
+      <c r="L44" t="inlineStr">
         <is>
           <t>+9 +8 +1</t>
         </is>
       </c>
-      <c r="L44" t="inlineStr">
+      <c r="M44" t="inlineStr">
         <is>
           <t>+9 +8 +1</t>
         </is>
       </c>
-      <c r="M44" t="inlineStr">
+      <c r="N44" t="inlineStr">
         <is>
           <t>+9 +8 +1</t>
         </is>
       </c>
-      <c r="N44" t="inlineStr">
+      <c r="O44" t="inlineStr">
         <is>
           <t>+9 +8 +1</t>
         </is>
       </c>
-      <c r="O44" t="inlineStr">
+      <c r="P44" t="inlineStr">
         <is>
           <t>5,8,18</t>
         </is>
       </c>
-      <c r="P44" t="inlineStr">
+      <c r="Q44" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="Q44" t="inlineStr">
+      <c r="R44" t="inlineStr">
         <is>
           <t>5,8,18</t>
         </is>
       </c>
-      <c r="R44" t="inlineStr">
+      <c r="S44" t="inlineStr">
         <is>
           <t>hhh</t>
         </is>
       </c>
-      <c r="S44" t="inlineStr">
+      <c r="T44" t="inlineStr">
         <is>
           <t>hhh</t>
         </is>
       </c>
-      <c r="Y44" t="inlineStr">
+      <c r="Z44" t="inlineStr">
         <is>
           <t>84232fe2-22f5-45db-88bb-eef3f04153de</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
+      <c r="AA44" t="inlineStr">
         <is>
           <t>6d0a6ef4-5dc4-42d5-bede-4afc6032e41e</t>
         </is>
@@ -3977,102 +4008,102 @@
           <t>1&lt;2,2~1+2</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
+      <c r="E45" t="inlineStr">
         <is>
           <t>– Demon Executioner</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
+      <c r="F45" t="inlineStr">
         <is>
           <t>Demon Slayer – Demon Executioner</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
+      <c r="G45" t="inlineStr">
         <is>
           <t>(~u)SS; (~d)SS</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
+      <c r="I45" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
+      <c r="J45" t="inlineStr">
         <is>
           <t>-7</t>
         </is>
       </c>
-      <c r="J45" t="inlineStr">
+      <c r="K45" t="inlineStr">
         <is>
           <t>+1 0 -12 -7</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
       <c r="L45" t="inlineStr">
         <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
           <t>+9 +8 +1 KD</t>
         </is>
       </c>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
       <c r="N45" t="inlineStr">
         <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
           <t>+9 +8 +1 KD</t>
         </is>
       </c>
-      <c r="O45" t="inlineStr">
+      <c r="P45" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="P45" t="inlineStr">
+      <c r="Q45" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="Q45" t="inlineStr">
+      <c r="R45" t="inlineStr">
         <is>
           <t>5,8,18,22</t>
         </is>
       </c>
-      <c r="R45" t="inlineStr">
+      <c r="S45" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="S45" t="inlineStr">
+      <c r="T45" t="inlineStr">
         <is>
           <t>hhhm</t>
         </is>
       </c>
-      <c r="V45" t="inlineStr">
+      <c r="W45" t="inlineStr">
         <is>
           <t>KND</t>
         </is>
       </c>
-      <c r="W45" t="inlineStr">
+      <c r="X45" t="inlineStr">
         <is>
           <t>Demon Executioner cancels the previous hit.; The Side Step cancels the Demon Executioner.</t>
         </is>
       </c>
-      <c r="Y45" t="inlineStr">
+      <c r="Z45" t="inlineStr">
         <is>
           <t>5b09c08e-09b3-4913-88a3-14d3bf367ca9</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
+      <c r="AA45" t="inlineStr">
         <is>
           <t>d179dfe4-126b-45c6-891e-6a2914df58cf</t>
         </is>
       </c>
-      <c r="AA45" t="inlineStr">
+      <c r="AB45" t="inlineStr">
         <is>
           <t>84232fe2-22f5-45db-88bb-eef3f04153de</t>
         </is>
@@ -4089,87 +4120,87 @@
           <t>f+1&lt;b+2,1</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
+      <c r="E46" t="inlineStr">
         <is>
           <t>Demon Massacre</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="F46" t="inlineStr">
         <is>
           <t>Demon Massacre</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr">
+      <c r="H46" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
+      <c r="I46" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
+      <c r="J46" t="inlineStr">
         <is>
           <t>+3 -1 -28</t>
         </is>
       </c>
-      <c r="J46" t="inlineStr">
+      <c r="K46" t="inlineStr">
         <is>
           <t>+3 -1 -28</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr">
+      <c r="L46" t="inlineStr">
         <is>
           <t>+9 +5 KD</t>
         </is>
       </c>
-      <c r="L46" t="inlineStr">
+      <c r="M46" t="inlineStr">
         <is>
           <t>+9 +5 KD</t>
         </is>
       </c>
-      <c r="M46" t="inlineStr">
+      <c r="N46" t="inlineStr">
         <is>
           <t>+9 +5 KD</t>
         </is>
       </c>
-      <c r="N46" t="inlineStr">
+      <c r="O46" t="inlineStr">
         <is>
           <t>+9 +5 KD</t>
         </is>
       </c>
-      <c r="O46" t="inlineStr">
+      <c r="P46" t="inlineStr">
         <is>
           <t>6,21,25</t>
         </is>
       </c>
-      <c r="P46" t="inlineStr">
+      <c r="Q46" t="inlineStr">
         <is>
           <t>52</t>
         </is>
       </c>
-      <c r="Q46" t="inlineStr">
+      <c r="R46" t="inlineStr">
         <is>
           <t>6,21,25</t>
         </is>
       </c>
-      <c r="R46" t="inlineStr">
+      <c r="S46" t="inlineStr">
         <is>
           <t>hmm</t>
         </is>
       </c>
-      <c r="S46" t="inlineStr">
+      <c r="T46" t="inlineStr">
         <is>
           <t>hmm</t>
         </is>
       </c>
-      <c r="Y46" t="inlineStr">
+      <c r="Z46" t="inlineStr">
         <is>
           <t>cf18e825-afa4-4f63-a13b-ab9f82dd60d8</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
+      <c r="AA46" t="inlineStr">
         <is>
           <t>ba68e2af-947f-46fd-bbd4-6f9748de5fa6</t>
         </is>
@@ -4186,92 +4217,92 @@
           <t>f+1&lt;b+2,4</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
+      <c r="E47" t="inlineStr">
         <is>
           <t>Demon Lair</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="F47" t="inlineStr">
         <is>
           <t>Demon Lair</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
+      <c r="H47" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
+      <c r="I47" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr">
+      <c r="J47" t="inlineStr">
         <is>
           <t>+3 -1 +3</t>
         </is>
       </c>
-      <c r="J47" t="inlineStr">
+      <c r="K47" t="inlineStr">
         <is>
           <t>+3 -1 +3</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr">
+      <c r="L47" t="inlineStr">
         <is>
           <t>+3 +5 KD</t>
         </is>
       </c>
-      <c r="L47" t="inlineStr">
+      <c r="M47" t="inlineStr">
         <is>
           <t>+3 +5 KD</t>
         </is>
       </c>
-      <c r="M47" t="inlineStr">
+      <c r="N47" t="inlineStr">
         <is>
           <t>+3 +5 KD</t>
         </is>
       </c>
-      <c r="N47" t="inlineStr">
+      <c r="O47" t="inlineStr">
         <is>
           <t>+3 +5 KD</t>
         </is>
       </c>
-      <c r="O47" t="inlineStr">
+      <c r="P47" t="inlineStr">
         <is>
           <t>6,21,30</t>
         </is>
       </c>
-      <c r="P47" t="inlineStr">
+      <c r="Q47" t="inlineStr">
         <is>
           <t>57</t>
         </is>
       </c>
-      <c r="Q47" t="inlineStr">
+      <c r="R47" t="inlineStr">
         <is>
           <t>6,21,30</t>
         </is>
       </c>
-      <c r="R47" t="inlineStr">
+      <c r="S47" t="inlineStr">
         <is>
           <t>hmm</t>
         </is>
       </c>
-      <c r="S47" t="inlineStr">
+      <c r="T47" t="inlineStr">
         <is>
           <t>hmm</t>
         </is>
       </c>
-      <c r="V47" t="inlineStr">
+      <c r="W47" t="inlineStr">
         <is>
           <t>GB</t>
         </is>
       </c>
-      <c r="Y47" t="inlineStr">
+      <c r="Z47" t="inlineStr">
         <is>
           <t>25172e0e-0977-4665-a19b-f6b673165143</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
+      <c r="AA47" t="inlineStr">
         <is>
           <t>ed33786a-081d-4f6b-a2b4-21493b6d9ec4</t>
         </is>
@@ -4288,87 +4319,87 @@
           <t>d+1</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
+      <c r="E48" t="inlineStr">
         <is>
           <t>Tile Splitter</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
+      <c r="F48" t="inlineStr">
         <is>
           <t>Tile Splitter</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr">
+      <c r="H48" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
+      <c r="I48" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
+      <c r="J48" t="inlineStr">
         <is>
           <t>-8</t>
         </is>
       </c>
-      <c r="J48" t="inlineStr">
+      <c r="K48" t="inlineStr">
         <is>
           <t>-8</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr">
+      <c r="L48" t="inlineStr">
         <is>
           <t>-8</t>
         </is>
       </c>
-      <c r="L48" t="inlineStr">
+      <c r="M48" t="inlineStr">
         <is>
           <t>-8</t>
         </is>
       </c>
-      <c r="M48" t="inlineStr">
+      <c r="N48" t="inlineStr">
         <is>
           <t>+4</t>
         </is>
       </c>
-      <c r="N48" t="inlineStr">
+      <c r="O48" t="inlineStr">
         <is>
           <t>+4</t>
         </is>
       </c>
-      <c r="O48" t="inlineStr">
+      <c r="P48" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="P48" t="inlineStr">
+      <c r="Q48" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q48" t="inlineStr">
+      <c r="R48" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="R48" t="inlineStr">
+      <c r="S48" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="S48" t="inlineStr">
+      <c r="T48" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="Y48" t="inlineStr">
+      <c r="Z48" t="inlineStr">
         <is>
           <t>dfd7ff87-faaf-4127-bbd9-4dca53b7da21</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
+      <c r="AA48" t="inlineStr">
         <is>
           <t>3dabca7e-8c1b-4b08-a5df-10b49c3ed200</t>
         </is>
@@ -4385,87 +4416,87 @@
           <t>d+1,2</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
+      <c r="E49" t="inlineStr">
         <is>
           <t>– Death Fist</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="F49" t="inlineStr">
         <is>
           <t>Tile Splitter – Death Fist</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
+      <c r="I49" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
+      <c r="J49" t="inlineStr">
         <is>
           <t>-17</t>
         </is>
       </c>
-      <c r="J49" t="inlineStr">
+      <c r="K49" t="inlineStr">
         <is>
           <t>-8 -17</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
       <c r="L49" t="inlineStr">
         <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
           <t>-8 KD</t>
         </is>
       </c>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
       <c r="N49" t="inlineStr">
         <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
           <t>+4 KD</t>
         </is>
       </c>
-      <c r="O49" t="inlineStr">
+      <c r="P49" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="P49" t="inlineStr">
+      <c r="Q49" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="Q49" t="inlineStr">
+      <c r="R49" t="inlineStr">
         <is>
           <t>15,26</t>
         </is>
       </c>
-      <c r="R49" t="inlineStr">
+      <c r="S49" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="S49" t="inlineStr">
+      <c r="T49" t="inlineStr">
         <is>
           <t>mm</t>
         </is>
       </c>
-      <c r="Y49" t="inlineStr">
+      <c r="Z49" t="inlineStr">
         <is>
           <t>8ce5cdd0-9ea6-4f83-8b25-9d0afc9413a0</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
+      <c r="AA49" t="inlineStr">
         <is>
           <t>7c6c71d8-5c87-4940-ad23-38ed00f6149f</t>
         </is>
       </c>
-      <c r="AA49" t="inlineStr">
+      <c r="AB49" t="inlineStr">
         <is>
           <t>dfd7ff87-faaf-4127-bbd9-4dca53b7da21</t>
         </is>
@@ -4482,97 +4513,97 @@
           <t>df+1,2</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr">
+      <c r="E50" t="inlineStr">
         <is>
           <t>Twin Pistons</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
+      <c r="F50" t="inlineStr">
         <is>
           <t>Twin Pistons</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr">
+      <c r="H50" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
+      <c r="I50" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
+      <c r="J50" t="inlineStr">
         <is>
           <t>-1 -27</t>
         </is>
       </c>
-      <c r="J50" t="inlineStr">
+      <c r="K50" t="inlineStr">
         <is>
           <t>-1 -27</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr">
+      <c r="L50" t="inlineStr">
         <is>
           <t>+9 KD</t>
         </is>
       </c>
-      <c r="L50" t="inlineStr">
+      <c r="M50" t="inlineStr">
         <is>
           <t>+9 KD</t>
         </is>
       </c>
-      <c r="M50" t="inlineStr">
+      <c r="N50" t="inlineStr">
         <is>
           <t>+9 KD</t>
         </is>
       </c>
-      <c r="N50" t="inlineStr">
+      <c r="O50" t="inlineStr">
         <is>
           <t>+9 KD</t>
         </is>
       </c>
-      <c r="O50" t="inlineStr">
+      <c r="P50" t="inlineStr">
         <is>
           <t>8,21</t>
         </is>
       </c>
-      <c r="P50" t="inlineStr">
+      <c r="Q50" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="Q50" t="inlineStr">
+      <c r="R50" t="inlineStr">
         <is>
           <t>8,21</t>
         </is>
       </c>
-      <c r="R50" t="inlineStr">
+      <c r="S50" t="inlineStr">
         <is>
           <t>mm</t>
         </is>
       </c>
-      <c r="S50" t="inlineStr">
+      <c r="T50" t="inlineStr">
         <is>
           <t>mm</t>
         </is>
       </c>
-      <c r="V50" t="inlineStr">
+      <c r="W50" t="inlineStr">
         <is>
           <t>JG</t>
         </is>
       </c>
-      <c r="X50" t="inlineStr">
+      <c r="Y50" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="Y50" t="inlineStr">
+      <c r="Z50" t="inlineStr">
         <is>
           <t>ec5ebcd7-e9bc-44b1-9b77-b91f9dc39f66</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
+      <c r="AA50" t="inlineStr">
         <is>
           <t>7cca0613-8eba-4b47-8c55-6bacc4cf6858</t>
         </is>
@@ -4589,41 +4620,36 @@
           <t>f,N,d,df+1</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
+      <c r="E51" t="inlineStr">
         <is>
           <t>Thunder Godfist</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
+      <c r="F51" t="inlineStr">
         <is>
           <t>Thunder Godfist</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr">
+      <c r="H51" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
+      <c r="I51" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
+      <c r="J51" t="inlineStr">
         <is>
           <t>-15</t>
         </is>
       </c>
-      <c r="J51" t="inlineStr">
+      <c r="K51" t="inlineStr">
         <is>
           <t>-15</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
       <c r="L51" t="inlineStr">
         <is>
           <t>KD</t>
@@ -4641,40 +4667,45 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
           <t>31</t>
         </is>
       </c>
-      <c r="P51" t="inlineStr">
+      <c r="Q51" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="Q51" t="inlineStr">
+      <c r="R51" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="R51" t="inlineStr">
+      <c r="S51" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="S51" t="inlineStr">
+      <c r="T51" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="W51" t="inlineStr">
+      <c r="X51" t="inlineStr">
         <is>
           <t>On a clean hit damage is 52.</t>
         </is>
       </c>
-      <c r="Y51" t="inlineStr">
+      <c r="Z51" t="inlineStr">
         <is>
           <t>fc9f67f0-efd6-442f-a3dd-40673e0f9273</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
+      <c r="AA51" t="inlineStr">
         <is>
           <t>e7f4b372-4384-43b9-9041-5008424e98fc</t>
         </is>
@@ -4691,41 +4722,36 @@
           <t>1+2</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr">
+      <c r="E52" t="inlineStr">
         <is>
           <t>Demon Breath</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
+      <c r="F52" t="inlineStr">
         <is>
           <t>Demon Breath</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr">
+      <c r="H52" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
+      <c r="I52" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr">
+      <c r="J52" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="J52" t="inlineStr">
+      <c r="K52" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
       <c r="L52" t="inlineStr">
         <is>
           <t>KD</t>
@@ -4743,40 +4769,45 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="P52" t="inlineStr">
+      <c r="Q52" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="Q52" t="inlineStr">
+      <c r="R52" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="R52" t="inlineStr">
+      <c r="S52" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="S52" t="inlineStr">
+      <c r="T52" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="V52" t="inlineStr">
+      <c r="W52" t="inlineStr">
         <is>
           <t>CF KNDc</t>
         </is>
       </c>
-      <c r="Y52" t="inlineStr">
+      <c r="Z52" t="inlineStr">
         <is>
           <t>03aed9fd-acbe-4903-a5f4-86fee6b288eb</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
+      <c r="AA52" t="inlineStr">
         <is>
           <t>52f48595-1a7d-43df-984b-9aa5af0acbe8</t>
         </is>
@@ -4793,51 +4824,46 @@
           <t>b+2</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
+      <c r="E53" t="inlineStr">
         <is>
           <t>Demon Boar</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
+      <c r="F53" t="inlineStr">
         <is>
           <t>Demon Boar</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr">
+      <c r="H53" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
+      <c r="I53" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr">
+      <c r="J53" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="J53" t="inlineStr">
+      <c r="K53" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr">
+      <c r="L53" t="inlineStr">
         <is>
           <t>+5</t>
         </is>
       </c>
-      <c r="L53" t="inlineStr">
+      <c r="M53" t="inlineStr">
         <is>
           <t>+5</t>
         </is>
       </c>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
       <c r="N53" t="inlineStr">
         <is>
           <t>KD</t>
@@ -4845,40 +4871,45 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="P53" t="inlineStr">
+      <c r="Q53" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="Q53" t="inlineStr">
+      <c r="R53" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="R53" t="inlineStr">
+      <c r="S53" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="S53" t="inlineStr">
+      <c r="T53" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="V53" t="inlineStr">
+      <c r="W53" t="inlineStr">
         <is>
           <t>MS KNDc</t>
         </is>
       </c>
-      <c r="Y53" t="inlineStr">
+      <c r="Z53" t="inlineStr">
         <is>
           <t>53f9e49f-94f7-4e5b-8dca-5cc758b156e9</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
+      <c r="AA53" t="inlineStr">
         <is>
           <t>95ab05b1-eee0-4967-802f-5ec8701cd87e</t>
         </is>
@@ -4895,87 +4926,87 @@
           <t>2,2</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr">
+      <c r="E54" t="inlineStr">
         <is>
           <t>Demon Backhand Spin</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
+      <c r="F54" t="inlineStr">
         <is>
           <t>Demon Backhand Spin</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr">
+      <c r="H54" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
+      <c r="I54" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr">
+      <c r="J54" t="inlineStr">
         <is>
           <t>0 -13</t>
         </is>
       </c>
-      <c r="J54" t="inlineStr">
+      <c r="K54" t="inlineStr">
         <is>
           <t>0 -13</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr">
+      <c r="L54" t="inlineStr">
         <is>
           <t>+9 -2</t>
         </is>
       </c>
-      <c r="L54" t="inlineStr">
+      <c r="M54" t="inlineStr">
         <is>
           <t>+9 -2</t>
         </is>
       </c>
-      <c r="M54" t="inlineStr">
+      <c r="N54" t="inlineStr">
         <is>
           <t>+9 -2</t>
         </is>
       </c>
-      <c r="N54" t="inlineStr">
+      <c r="O54" t="inlineStr">
         <is>
           <t>+9 -2</t>
         </is>
       </c>
-      <c r="O54" t="inlineStr">
+      <c r="P54" t="inlineStr">
         <is>
           <t>12,21</t>
         </is>
       </c>
-      <c r="P54" t="inlineStr">
+      <c r="Q54" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="Q54" t="inlineStr">
+      <c r="R54" t="inlineStr">
         <is>
           <t>12,21</t>
         </is>
       </c>
-      <c r="R54" t="inlineStr">
+      <c r="S54" t="inlineStr">
         <is>
           <t>hh</t>
         </is>
       </c>
-      <c r="S54" t="inlineStr">
+      <c r="T54" t="inlineStr">
         <is>
           <t>hh</t>
         </is>
       </c>
-      <c r="Y54" t="inlineStr">
+      <c r="Z54" t="inlineStr">
         <is>
           <t>0a027bcb-93fd-4ff0-8ccf-f195fc7eff06</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
+      <c r="AA54" t="inlineStr">
         <is>
           <t>d1e026ec-e70f-4352-ac90-f4a4d9bd194a</t>
         </is>
@@ -4992,87 +5023,87 @@
           <t>f+2</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr">
+      <c r="E55" t="inlineStr">
         <is>
           <t>Demon Backhand</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
+      <c r="F55" t="inlineStr">
         <is>
           <t>Demon Backhand</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr">
+      <c r="H55" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
+      <c r="I55" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr">
+      <c r="J55" t="inlineStr">
         <is>
           <t>-13</t>
         </is>
       </c>
-      <c r="J55" t="inlineStr">
+      <c r="K55" t="inlineStr">
         <is>
           <t>-13</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr">
+      <c r="L55" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="L55" t="inlineStr">
+      <c r="M55" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="M55" t="inlineStr">
+      <c r="N55" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="N55" t="inlineStr">
+      <c r="O55" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="O55" t="inlineStr">
+      <c r="P55" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="P55" t="inlineStr">
+      <c r="Q55" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="Q55" t="inlineStr">
+      <c r="R55" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="R55" t="inlineStr">
+      <c r="S55" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="S55" t="inlineStr">
+      <c r="T55" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="Y55" t="inlineStr">
+      <c r="Z55" t="inlineStr">
         <is>
           <t>def5efd8-0361-461e-ba4d-56503556be0d</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
+      <c r="AA55" t="inlineStr">
         <is>
           <t>114d3f24-d4a3-480e-99f9-4ccee1b5e132</t>
         </is>
@@ -5089,102 +5120,102 @@
           <t>f+2~1+2</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr">
+      <c r="E56" t="inlineStr">
         <is>
           <t>– Demon Breath</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
+      <c r="F56" t="inlineStr">
         <is>
           <t>Demon Backhand – Demon Breath</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr">
+      <c r="H56" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
+      <c r="I56" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr">
+      <c r="J56" t="inlineStr">
         <is>
           <t>-7</t>
         </is>
       </c>
-      <c r="J56" t="inlineStr">
+      <c r="K56" t="inlineStr">
         <is>
           <t>-13 -7</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
       <c r="L56" t="inlineStr">
         <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
           <t>-2 KD</t>
         </is>
       </c>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
       <c r="N56" t="inlineStr">
         <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
           <t>-2 KD</t>
         </is>
       </c>
-      <c r="O56" t="inlineStr">
+      <c r="P56" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="P56" t="inlineStr">
+      <c r="Q56" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="Q56" t="inlineStr">
+      <c r="R56" t="inlineStr">
         <is>
           <t>21,25</t>
         </is>
       </c>
-      <c r="R56" t="inlineStr">
+      <c r="S56" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="S56" t="inlineStr">
+      <c r="T56" t="inlineStr">
         <is>
           <t>hm</t>
         </is>
       </c>
-      <c r="V56" t="inlineStr">
+      <c r="W56" t="inlineStr">
         <is>
           <t>KND</t>
         </is>
       </c>
-      <c r="W56" t="inlineStr">
+      <c r="X56" t="inlineStr">
         <is>
           <t>Demon Executioner cancels the previous hit.</t>
         </is>
       </c>
-      <c r="Y56" t="inlineStr">
+      <c r="Z56" t="inlineStr">
         <is>
           <t>6bc7980e-339b-4862-a189-7a7c97ad654b</t>
         </is>
       </c>
-      <c r="Z56" t="inlineStr">
+      <c r="AA56" t="inlineStr">
         <is>
           <t>52149449-5e95-4e94-ae94-d23c918581ec</t>
         </is>
       </c>
-      <c r="AA56" t="inlineStr">
+      <c r="AB56" t="inlineStr">
         <is>
           <t>def5efd8-0361-461e-ba4d-56503556be0d</t>
         </is>
@@ -5201,41 +5232,36 @@
           <t>f,f+2</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr">
+      <c r="E57" t="inlineStr">
         <is>
           <t>Demon Godfist</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
+      <c r="F57" t="inlineStr">
         <is>
           <t>Demon Godfist</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr">
+      <c r="H57" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
+      <c r="I57" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr">
+      <c r="J57" t="inlineStr">
         <is>
           <t>-16</t>
         </is>
       </c>
-      <c r="J57" t="inlineStr">
+      <c r="K57" t="inlineStr">
         <is>
           <t>-16</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
       <c r="L57" t="inlineStr">
         <is>
           <t>KD</t>
@@ -5253,45 +5279,50 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="P57" t="inlineStr">
+      <c r="Q57" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="Q57" t="inlineStr">
+      <c r="R57" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="R57" t="inlineStr">
+      <c r="S57" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="S57" t="inlineStr">
+      <c r="T57" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="V57" t="inlineStr">
+      <c r="W57" t="inlineStr">
         <is>
           <t>JG</t>
         </is>
       </c>
-      <c r="X57" t="inlineStr">
+      <c r="Y57" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="Y57" t="inlineStr">
+      <c r="Z57" t="inlineStr">
         <is>
           <t>7e41126e-b556-4341-90e6-de9a17e27e63</t>
         </is>
       </c>
-      <c r="Z57" t="inlineStr">
+      <c r="AA57" t="inlineStr">
         <is>
           <t>d757091e-2404-4579-8d58-622845ab4257</t>
         </is>
@@ -5308,41 +5339,36 @@
           <t>f,N,d,df+2</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr">
+      <c r="E58" t="inlineStr">
         <is>
           <t>Wind Godfist</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr">
+      <c r="F58" t="inlineStr">
         <is>
           <t>Wind Godfist</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr">
+      <c r="H58" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
+      <c r="I58" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr">
+      <c r="J58" t="inlineStr">
         <is>
           <t>-10</t>
         </is>
       </c>
-      <c r="J58" t="inlineStr">
+      <c r="K58" t="inlineStr">
         <is>
           <t>-10</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
       <c r="L58" t="inlineStr">
         <is>
           <t>KD</t>
@@ -5360,45 +5386,50 @@
       </c>
       <c r="O58" t="inlineStr">
         <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="P58" t="inlineStr">
+      <c r="Q58" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="Q58" t="inlineStr">
+      <c r="R58" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="R58" t="inlineStr">
+      <c r="S58" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="S58" t="inlineStr">
+      <c r="T58" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="V58" t="inlineStr">
+      <c r="W58" t="inlineStr">
         <is>
           <t>JG</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr">
+      <c r="Y58" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="Y58" t="inlineStr">
+      <c r="Z58" t="inlineStr">
         <is>
           <t>e9cc8d24-94c5-4666-904c-ce10afa52191</t>
         </is>
       </c>
-      <c r="Z58" t="inlineStr">
+      <c r="AA58" t="inlineStr">
         <is>
           <t>38165070-f819-4dee-a042-75a435e0973a</t>
         </is>
@@ -5415,41 +5446,36 @@
           <t>f~N~d~df+2</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr">
+      <c r="E59" t="inlineStr">
         <is>
           <t>Electric Wind Godfist</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr">
+      <c r="F59" t="inlineStr">
         <is>
           <t>Electric Wind Godfist</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr">
+      <c r="H59" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
+      <c r="I59" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr">
+      <c r="J59" t="inlineStr">
         <is>
           <t>+4</t>
         </is>
       </c>
-      <c r="J59" t="inlineStr">
+      <c r="K59" t="inlineStr">
         <is>
           <t>+4</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
       <c r="L59" t="inlineStr">
         <is>
           <t>KD</t>
@@ -5467,45 +5493,50 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="P59" t="inlineStr">
+      <c r="Q59" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="Q59" t="inlineStr">
+      <c r="R59" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="R59" t="inlineStr">
+      <c r="S59" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="S59" t="inlineStr">
+      <c r="T59" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="V59" t="inlineStr">
+      <c r="W59" t="inlineStr">
         <is>
           <t>JG GB</t>
         </is>
       </c>
-      <c r="X59" t="inlineStr">
+      <c r="Y59" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="Y59" t="inlineStr">
+      <c r="Z59" t="inlineStr">
         <is>
           <t>ca860141-c30a-4429-bc3f-ee8db6a8c1c4</t>
         </is>
       </c>
-      <c r="Z59" t="inlineStr">
+      <c r="AA59" t="inlineStr">
         <is>
           <t>6830a895-2438-4045-8b3c-c8372219b444</t>
         </is>
@@ -5522,41 +5553,36 @@
           <t>qcf+2</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr">
+      <c r="E60" t="inlineStr">
         <is>
           <t>Deathfist</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr">
+      <c r="F60" t="inlineStr">
         <is>
           <t>Deathfist</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr">
+      <c r="H60" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
+      <c r="I60" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr">
+      <c r="J60" t="inlineStr">
         <is>
           <t>-17</t>
         </is>
       </c>
-      <c r="J60" t="inlineStr">
+      <c r="K60" t="inlineStr">
         <is>
           <t>-17</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
       <c r="L60" t="inlineStr">
         <is>
           <t>KD</t>
@@ -5574,35 +5600,40 @@
       </c>
       <c r="O60" t="inlineStr">
         <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="P60" t="inlineStr">
+      <c r="Q60" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="Q60" t="inlineStr">
+      <c r="R60" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="R60" t="inlineStr">
+      <c r="S60" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="S60" t="inlineStr">
+      <c r="T60" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="Y60" t="inlineStr">
+      <c r="Z60" t="inlineStr">
         <is>
           <t>93bd464b-add8-4400-9fa2-07651b194151</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
+      <c r="AA60" t="inlineStr">
         <is>
           <t>1ac6d532-3b56-49ac-a240-b0459bec630a</t>
         </is>
@@ -5619,51 +5650,46 @@
           <t>WS+2</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr">
+      <c r="E61" t="inlineStr">
         <is>
           <t>Dark Thrust</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr">
+      <c r="F61" t="inlineStr">
         <is>
           <t>Dark Thrust</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr">
+      <c r="H61" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
+      <c r="I61" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr">
+      <c r="J61" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="J61" t="inlineStr">
+      <c r="K61" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr">
+      <c r="L61" t="inlineStr">
         <is>
           <t>+4</t>
         </is>
       </c>
-      <c r="L61" t="inlineStr">
+      <c r="M61" t="inlineStr">
         <is>
           <t>+4</t>
         </is>
       </c>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
       <c r="N61" t="inlineStr">
         <is>
           <t>KD</t>
@@ -5671,40 +5697,45 @@
       </c>
       <c r="O61" t="inlineStr">
         <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="P61" t="inlineStr">
+      <c r="Q61" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="Q61" t="inlineStr">
+      <c r="R61" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="R61" t="inlineStr">
+      <c r="S61" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="S61" t="inlineStr">
+      <c r="T61" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="V61" t="inlineStr">
+      <c r="W61" t="inlineStr">
         <is>
           <t>MS CSc</t>
         </is>
       </c>
-      <c r="Y61" t="inlineStr">
+      <c r="Z61" t="inlineStr">
         <is>
           <t>5ea71dae-6d6f-4d22-a793-286c4e016413</t>
         </is>
       </c>
-      <c r="Z61" t="inlineStr">
+      <c r="AA61" t="inlineStr">
         <is>
           <t>cabb429b-8362-45b7-936e-5184c726b303</t>
         </is>
@@ -5721,41 +5752,36 @@
           <t>f,f+3</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr">
+      <c r="E62" t="inlineStr">
         <is>
           <t>Split Axe Kick</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr">
+      <c r="F62" t="inlineStr">
         <is>
           <t>Split Axe Kick</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr">
+      <c r="H62" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
+      <c r="I62" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr">
+      <c r="J62" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="J62" t="inlineStr">
+      <c r="K62" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
       <c r="L62" t="inlineStr">
         <is>
           <t>KD</t>
@@ -5773,40 +5799,45 @@
       </c>
       <c r="O62" t="inlineStr">
         <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="P62" t="inlineStr">
+      <c r="Q62" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="Q62" t="inlineStr">
+      <c r="R62" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="R62" t="inlineStr">
+      <c r="S62" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="S62" t="inlineStr">
+      <c r="T62" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="V62" t="inlineStr">
+      <c r="W62" t="inlineStr">
         <is>
           <t>GB</t>
         </is>
       </c>
-      <c r="Y62" t="inlineStr">
+      <c r="Z62" t="inlineStr">
         <is>
           <t>fc8a8eb1-ad44-4894-8dbe-7ef55b382149</t>
         </is>
       </c>
-      <c r="Z62" t="inlineStr">
+      <c r="AA62" t="inlineStr">
         <is>
           <t>20da6fcd-32b8-4d8f-8cb5-1fe9f89db475</t>
         </is>
@@ -5830,39 +5861,39 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
+          <t>f,f,f+3</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
           <t>Leaping Slash Kick</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr">
+      <c r="F63" t="inlineStr">
         <is>
           <t>Leaping Slash Kick</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr">
+      <c r="H63" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
+      <c r="I63" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr">
+      <c r="J63" t="inlineStr">
         <is>
           <t>+17</t>
         </is>
       </c>
-      <c r="J63" t="inlineStr">
+      <c r="K63" t="inlineStr">
         <is>
           <t>+17</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
       <c r="L63" t="inlineStr">
         <is>
           <t>KD</t>
@@ -5880,40 +5911,45 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="P63" t="inlineStr">
+      <c r="Q63" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="Q63" t="inlineStr">
+      <c r="R63" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="R63" t="inlineStr">
+      <c r="S63" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="S63" t="inlineStr">
+      <c r="T63" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="V63" t="inlineStr">
+      <c r="W63" t="inlineStr">
         <is>
           <t>GB</t>
         </is>
       </c>
-      <c r="Y63" t="inlineStr">
+      <c r="Z63" t="inlineStr">
         <is>
           <t>19d63d7e-c9fa-4752-b05b-1568ef1eff12</t>
         </is>
       </c>
-      <c r="Z63" t="inlineStr">
+      <c r="AA63" t="inlineStr">
         <is>
           <t>292e8322-a299-4d25-9f86-079da27de238</t>
         </is>
@@ -5930,41 +5966,36 @@
           <t>f,N,d,df+3</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr">
+      <c r="E64" t="inlineStr">
         <is>
           <t>Demon Gut Kick</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr">
+      <c r="F64" t="inlineStr">
         <is>
           <t>Demon Gut Kick</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr">
+      <c r="H64" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
+      <c r="I64" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr">
+      <c r="J64" t="inlineStr">
         <is>
           <t>+14</t>
         </is>
       </c>
-      <c r="J64" t="inlineStr">
+      <c r="K64" t="inlineStr">
         <is>
           <t>+14</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
       <c r="L64" t="inlineStr">
         <is>
           <t>KD</t>
@@ -5982,40 +6013,45 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
           <t>35</t>
         </is>
       </c>
-      <c r="P64" t="inlineStr">
+      <c r="Q64" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="Q64" t="inlineStr">
+      <c r="R64" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="R64" t="inlineStr">
+      <c r="S64" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="S64" t="inlineStr">
+      <c r="T64" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="V64" t="inlineStr">
+      <c r="W64" t="inlineStr">
         <is>
           <t>GB</t>
         </is>
       </c>
-      <c r="Y64" t="inlineStr">
+      <c r="Z64" t="inlineStr">
         <is>
           <t>4021c60b-e178-47a2-89e4-4cfa7ca28e40</t>
         </is>
       </c>
-      <c r="Z64" t="inlineStr">
+      <c r="AA64" t="inlineStr">
         <is>
           <t>2f13ea2c-55ea-482d-aefb-3221ba69b317</t>
         </is>
@@ -6032,41 +6068,36 @@
           <t>f,N,d,DF+3</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr">
+      <c r="E65" t="inlineStr">
         <is>
           <t>Demon Slice Kick</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr">
+      <c r="F65" t="inlineStr">
         <is>
           <t>Demon Slice Kick</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr">
+      <c r="H65" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
+      <c r="I65" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr">
+      <c r="J65" t="inlineStr">
         <is>
           <t>-14</t>
         </is>
       </c>
-      <c r="J65" t="inlineStr">
+      <c r="K65" t="inlineStr">
         <is>
           <t>-14</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
       <c r="L65" t="inlineStr">
         <is>
           <t>KD</t>
@@ -6084,35 +6115,40 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
           <t>21</t>
         </is>
       </c>
-      <c r="P65" t="inlineStr">
+      <c r="Q65" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="Q65" t="inlineStr">
+      <c r="R65" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="R65" t="inlineStr">
+      <c r="S65" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="S65" t="inlineStr">
+      <c r="T65" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="Y65" t="inlineStr">
+      <c r="Z65" t="inlineStr">
         <is>
           <t>c3570215-9bb3-404f-b1e9-756b8c8580bb</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr">
+      <c r="AA65" t="inlineStr">
         <is>
           <t>eceddea0-38d0-46b1-852b-31320d807156</t>
         </is>
@@ -6129,97 +6165,97 @@
           <t>uf+3,4</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr">
+      <c r="E66" t="inlineStr">
         <is>
           <t>Hell Axe</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr">
+      <c r="F66" t="inlineStr">
         <is>
           <t>Hell Axe</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr">
+      <c r="H66" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
+      <c r="I66" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr">
+      <c r="J66" t="inlineStr">
         <is>
           <t>-6 +7</t>
         </is>
       </c>
-      <c r="J66" t="inlineStr">
+      <c r="K66" t="inlineStr">
         <is>
           <t>-6 +7</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr">
+      <c r="L66" t="inlineStr">
         <is>
           <t>KD KD</t>
         </is>
       </c>
-      <c r="L66" t="inlineStr">
+      <c r="M66" t="inlineStr">
         <is>
           <t>KD KD</t>
         </is>
       </c>
-      <c r="M66" t="inlineStr">
+      <c r="N66" t="inlineStr">
         <is>
           <t>KD KD</t>
         </is>
       </c>
-      <c r="N66" t="inlineStr">
+      <c r="O66" t="inlineStr">
         <is>
           <t>KD KD</t>
         </is>
       </c>
-      <c r="O66" t="inlineStr">
+      <c r="P66" t="inlineStr">
         <is>
           <t>17,22</t>
         </is>
       </c>
-      <c r="P66" t="inlineStr">
+      <c r="Q66" t="inlineStr">
         <is>
           <t>39</t>
         </is>
       </c>
-      <c r="Q66" t="inlineStr">
+      <c r="R66" t="inlineStr">
         <is>
           <t>17,22</t>
         </is>
       </c>
-      <c r="R66" t="inlineStr">
+      <c r="S66" t="inlineStr">
         <is>
           <t>mh</t>
         </is>
       </c>
-      <c r="S66" t="inlineStr">
+      <c r="T66" t="inlineStr">
         <is>
           <t>mh</t>
         </is>
       </c>
-      <c r="V66" t="inlineStr">
+      <c r="W66" t="inlineStr">
         <is>
           <t>GB</t>
         </is>
       </c>
-      <c r="W66" t="inlineStr">
+      <c r="X66" t="inlineStr">
         <is>
           <t>On neutral block the 2nd hit will connect.</t>
         </is>
       </c>
-      <c r="Y66" t="inlineStr">
+      <c r="Z66" t="inlineStr">
         <is>
           <t>9e590449-e10d-4d5e-a302-010249025523</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr">
+      <c r="AA66" t="inlineStr">
         <is>
           <t>cb2e07ce-106c-40a9-bc4e-a63422db65e8</t>
         </is>
@@ -6236,52 +6272,52 @@
           <t>u+4</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr">
+      <c r="E67" t="inlineStr">
         <is>
           <t>Hop Kick</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr">
+      <c r="F67" t="inlineStr">
         <is>
           <t>Hop Kick</t>
         </is>
       </c>
-      <c r="O67" t="inlineStr">
+      <c r="P67" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="P67" t="inlineStr">
+      <c r="Q67" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q67" t="inlineStr">
+      <c r="R67" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="R67" t="inlineStr">
+      <c r="S67" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="S67" t="inlineStr">
+      <c r="T67" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="V67" t="inlineStr">
+      <c r="W67" t="inlineStr">
         <is>
           <t>JG</t>
         </is>
       </c>
-      <c r="Y67" t="inlineStr">
+      <c r="Z67" t="inlineStr">
         <is>
           <t>871b2c24-ff65-4e92-b6e1-44b2616547a8</t>
         </is>
       </c>
-      <c r="Z67" t="inlineStr">
+      <c r="AA67" t="inlineStr">
         <is>
           <t>69de16a3-4a9e-40f4-ad50-e92f48c505db</t>
         </is>
@@ -6298,87 +6334,87 @@
           <t>uf+4,4</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr">
+      <c r="E68" t="inlineStr">
         <is>
           <t>Rising Sun</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr">
+      <c r="F68" t="inlineStr">
         <is>
           <t>Rising Sun</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr">
+      <c r="H68" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
+      <c r="I68" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr">
+      <c r="J68" t="inlineStr">
         <is>
           <t>-26 -6</t>
         </is>
       </c>
-      <c r="J68" t="inlineStr">
+      <c r="K68" t="inlineStr">
         <is>
           <t>-26 -6</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr">
+      <c r="L68" t="inlineStr">
         <is>
           <t>KD KD</t>
         </is>
       </c>
-      <c r="L68" t="inlineStr">
+      <c r="M68" t="inlineStr">
         <is>
           <t>KD KD</t>
         </is>
       </c>
-      <c r="M68" t="inlineStr">
+      <c r="N68" t="inlineStr">
         <is>
           <t>KD KD</t>
         </is>
       </c>
-      <c r="N68" t="inlineStr">
+      <c r="O68" t="inlineStr">
         <is>
           <t>KD KD</t>
         </is>
       </c>
-      <c r="O68" t="inlineStr">
+      <c r="P68" t="inlineStr">
         <is>
           <t>25,15</t>
         </is>
       </c>
-      <c r="P68" t="inlineStr">
+      <c r="Q68" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="Q68" t="inlineStr">
+      <c r="R68" t="inlineStr">
         <is>
           <t>25,15</t>
         </is>
       </c>
-      <c r="R68" t="inlineStr">
+      <c r="S68" t="inlineStr">
         <is>
           <t>hL</t>
         </is>
       </c>
-      <c r="S68" t="inlineStr">
+      <c r="T68" t="inlineStr">
         <is>
           <t>hL</t>
         </is>
       </c>
-      <c r="Y68" t="inlineStr">
+      <c r="Z68" t="inlineStr">
         <is>
           <t>6df4b756-97b1-4fcf-b8ff-a29527737049</t>
         </is>
       </c>
-      <c r="Z68" t="inlineStr">
+      <c r="AA68" t="inlineStr">
         <is>
           <t>e2b554ce-7879-4d5d-9a63-0ff018f5d5ef</t>
         </is>
@@ -6402,85 +6438,90 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
+          <t>f,N,d,df,f+4&lt;4; WS+4&lt;4</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
           <t>Delay Tsunami Kick</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr">
+      <c r="F69" t="inlineStr">
         <is>
           <t>Delay Tsunami Kick</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr">
+      <c r="H69" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
+      <c r="I69" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr">
+      <c r="J69" t="inlineStr">
         <is>
           <t>-5 -15</t>
         </is>
       </c>
-      <c r="J69" t="inlineStr">
+      <c r="K69" t="inlineStr">
         <is>
           <t>-5 -15</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr">
+      <c r="L69" t="inlineStr">
         <is>
           <t>+6 -4</t>
         </is>
       </c>
-      <c r="L69" t="inlineStr">
+      <c r="M69" t="inlineStr">
         <is>
           <t>+6 -4</t>
         </is>
       </c>
-      <c r="M69" t="inlineStr">
+      <c r="N69" t="inlineStr">
         <is>
           <t>+6 -4</t>
         </is>
       </c>
-      <c r="N69" t="inlineStr">
+      <c r="O69" t="inlineStr">
         <is>
           <t>+6 -4</t>
         </is>
       </c>
-      <c r="O69" t="inlineStr">
+      <c r="P69" t="inlineStr">
         <is>
           <t>12,18</t>
         </is>
       </c>
-      <c r="P69" t="inlineStr">
+      <c r="Q69" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="Q69" t="inlineStr">
+      <c r="R69" t="inlineStr">
         <is>
           <t>12,18</t>
         </is>
       </c>
-      <c r="R69" t="inlineStr">
+      <c r="S69" t="inlineStr">
         <is>
           <t>mm</t>
         </is>
       </c>
-      <c r="S69" t="inlineStr">
+      <c r="T69" t="inlineStr">
         <is>
           <t>mm</t>
         </is>
       </c>
-      <c r="Y69" t="inlineStr">
+      <c r="Z69" t="inlineStr">
         <is>
           <t>e76e6c9a-0442-440c-883d-38289c144dd6</t>
         </is>
       </c>
-      <c r="Z69" t="inlineStr">
+      <c r="AA69" t="inlineStr">
         <is>
           <t>2acd50c8-1536-44db-bd07-34af0327aeda</t>
         </is>
@@ -6497,51 +6538,46 @@
           <t>f,N,d,DF+4</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr">
+      <c r="E70" t="inlineStr">
         <is>
           <t>Hell Sweep</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr">
+      <c r="F70" t="inlineStr">
         <is>
           <t>Hell Sweep</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr">
+      <c r="H70" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
+      <c r="I70" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr">
+      <c r="J70" t="inlineStr">
         <is>
           <t>-23</t>
         </is>
       </c>
-      <c r="J70" t="inlineStr">
+      <c r="K70" t="inlineStr">
         <is>
           <t>-23</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr">
+      <c r="L70" t="inlineStr">
         <is>
           <t>+5</t>
         </is>
       </c>
-      <c r="L70" t="inlineStr">
+      <c r="M70" t="inlineStr">
         <is>
           <t>+5</t>
         </is>
       </c>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
       <c r="N70" t="inlineStr">
         <is>
           <t>KD</t>
@@ -6549,45 +6585,50 @@
       </c>
       <c r="O70" t="inlineStr">
         <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="P70" t="inlineStr">
+      <c r="Q70" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q70" t="inlineStr">
+      <c r="R70" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="R70" t="inlineStr">
+      <c r="S70" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="S70" t="inlineStr">
+      <c r="T70" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="V70" t="inlineStr">
+      <c r="W70" t="inlineStr">
         <is>
           <t>JGc BS KS</t>
         </is>
       </c>
-      <c r="W70" t="inlineStr">
+      <c r="X70" t="inlineStr">
         <is>
           <t>The Hell Sweeps causes Knee Drop Stun, you can still block the next Hell Sweep. Causing Heihachi to Low Block Stagger.</t>
         </is>
       </c>
-      <c r="Y70" t="inlineStr">
+      <c r="Z70" t="inlineStr">
         <is>
           <t>671ef239-098f-4d0b-bfd2-166912e226ae</t>
         </is>
       </c>
-      <c r="Z70" t="inlineStr">
+      <c r="AA70" t="inlineStr">
         <is>
           <t>e8203366-e9e8-438e-b327-bfc5e0436bff</t>
         </is>
@@ -6604,72 +6645,72 @@
           <t>f,N,d,DF+4,N+4</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr">
+      <c r="E71" t="inlineStr">
         <is>
           <t>– Rising Kick</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr">
+      <c r="F71" t="inlineStr">
         <is>
           <t>Hell Sweep – Rising Kick</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
+      <c r="I71" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="J71" t="inlineStr">
+      <c r="K71" t="inlineStr">
         <is>
           <t>-23</t>
         </is>
       </c>
-      <c r="L71" t="inlineStr">
+      <c r="M71" t="inlineStr">
         <is>
           <t>+5</t>
         </is>
       </c>
-      <c r="N71" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
       <c r="O71" t="inlineStr">
         <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="P71" t="inlineStr">
+      <c r="Q71" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="Q71" t="inlineStr">
+      <c r="R71" t="inlineStr">
         <is>
           <t>15,14</t>
         </is>
       </c>
-      <c r="R71" t="inlineStr">
+      <c r="S71" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="S71" t="inlineStr">
+      <c r="T71" t="inlineStr">
         <is>
           <t>Lm</t>
         </is>
       </c>
-      <c r="Y71" t="inlineStr">
+      <c r="Z71" t="inlineStr">
         <is>
           <t>98628fce-5a47-4ba1-a41a-f455273494d4</t>
         </is>
       </c>
-      <c r="Z71" t="inlineStr">
+      <c r="AA71" t="inlineStr">
         <is>
           <t>1fb2c0d5-9f21-48d7-8e53-43577238f9ad</t>
         </is>
       </c>
-      <c r="AA71" t="inlineStr">
+      <c r="AB71" t="inlineStr">
         <is>
           <t>671ef239-098f-4d0b-bfd2-166912e226ae</t>
         </is>
@@ -6686,87 +6727,87 @@
           <t>f,N,d,DF+4,N+4,4</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr">
+      <c r="E72" t="inlineStr">
         <is>
           <t>– Tsunami Kick</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr">
+      <c r="F72" t="inlineStr">
         <is>
           <t>Hell Sweep – Tsunami Kick</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
+      <c r="I72" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="I72" t="inlineStr">
+      <c r="J72" t="inlineStr">
         <is>
           <t>-3 -16</t>
         </is>
       </c>
-      <c r="J72" t="inlineStr">
+      <c r="K72" t="inlineStr">
         <is>
           <t>-23 -3 -16</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr">
+      <c r="L72" t="inlineStr">
         <is>
           <t>+8 -5</t>
         </is>
       </c>
-      <c r="L72" t="inlineStr">
+      <c r="M72" t="inlineStr">
         <is>
           <t>+5 +8 -5</t>
         </is>
       </c>
-      <c r="M72" t="inlineStr">
+      <c r="N72" t="inlineStr">
         <is>
           <t>+8 -5</t>
         </is>
       </c>
-      <c r="N72" t="inlineStr">
+      <c r="O72" t="inlineStr">
         <is>
           <t>KD +8 -5</t>
         </is>
       </c>
-      <c r="O72" t="inlineStr">
+      <c r="P72" t="inlineStr">
         <is>
           <t>14,21</t>
         </is>
       </c>
-      <c r="P72" t="inlineStr">
+      <c r="Q72" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="Q72" t="inlineStr">
+      <c r="R72" t="inlineStr">
         <is>
           <t>15,14,21</t>
         </is>
       </c>
-      <c r="R72" t="inlineStr">
+      <c r="S72" t="inlineStr">
         <is>
           <t>mm</t>
         </is>
       </c>
-      <c r="S72" t="inlineStr">
+      <c r="T72" t="inlineStr">
         <is>
           <t>Lmm</t>
         </is>
       </c>
-      <c r="Y72" t="inlineStr">
+      <c r="Z72" t="inlineStr">
         <is>
           <t>f9614d72-ba63-4105-a42b-1bcf84c119a2</t>
         </is>
       </c>
-      <c r="Z72" t="inlineStr">
+      <c r="AA72" t="inlineStr">
         <is>
           <t>a35a84a5-de8a-4232-8e83-56571959cd5c</t>
         </is>
       </c>
-      <c r="AA72" t="inlineStr">
+      <c r="AB72" t="inlineStr">
         <is>
           <t>671ef239-098f-4d0b-bfd2-166912e226ae</t>
         </is>
@@ -6783,92 +6824,92 @@
           <t>f,N,d,DF+4,N+1</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr">
+      <c r="E73" t="inlineStr">
         <is>
           <t>– Thunder Godfist</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr">
+      <c r="F73" t="inlineStr">
         <is>
           <t>Hell Sweep – Thunder Godfist</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
+      <c r="I73" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="I73" t="inlineStr">
+      <c r="J73" t="inlineStr">
         <is>
           <t>-12</t>
         </is>
       </c>
-      <c r="J73" t="inlineStr">
+      <c r="K73" t="inlineStr">
         <is>
           <t>-23 -12</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
       <c r="L73" t="inlineStr">
         <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
           <t>+5 KD</t>
         </is>
       </c>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
       <c r="N73" t="inlineStr">
         <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
           <t>KD KD</t>
         </is>
       </c>
-      <c r="O73" t="inlineStr">
+      <c r="P73" t="inlineStr">
         <is>
           <t>37</t>
         </is>
       </c>
-      <c r="P73" t="inlineStr">
+      <c r="Q73" t="inlineStr">
         <is>
           <t>37</t>
         </is>
       </c>
-      <c r="Q73" t="inlineStr">
+      <c r="R73" t="inlineStr">
         <is>
           <t>15,37</t>
         </is>
       </c>
-      <c r="R73" t="inlineStr">
+      <c r="S73" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="S73" t="inlineStr">
+      <c r="T73" t="inlineStr">
         <is>
           <t>Lm</t>
         </is>
       </c>
-      <c r="W73" t="inlineStr">
+      <c r="X73" t="inlineStr">
         <is>
           <t>Damage will be 28 if only the Thunder Godfist hits.</t>
         </is>
       </c>
-      <c r="Y73" t="inlineStr">
+      <c r="Z73" t="inlineStr">
         <is>
           <t>ade9fdb2-ebe5-4010-9af6-22122fafbfa7</t>
         </is>
       </c>
-      <c r="Z73" t="inlineStr">
+      <c r="AA73" t="inlineStr">
         <is>
           <t>61aa2c38-48e3-4bb0-9132-9eb7abc72882</t>
         </is>
       </c>
-      <c r="AA73" t="inlineStr">
+      <c r="AB73" t="inlineStr">
         <is>
           <t>671ef239-098f-4d0b-bfd2-166912e226ae</t>
         </is>
@@ -6885,92 +6926,92 @@
           <t>f,N,d,DF+4,4</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr">
+      <c r="E74" t="inlineStr">
         <is>
           <t>– Hell Sweep</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr">
+      <c r="F74" t="inlineStr">
         <is>
           <t>Hell Sweep – Hell Sweep</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
+      <c r="I74" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr">
+      <c r="J74" t="inlineStr">
         <is>
           <t>-14</t>
         </is>
       </c>
-      <c r="J74" t="inlineStr">
+      <c r="K74" t="inlineStr">
         <is>
           <t>-23 -14</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
       <c r="L74" t="inlineStr">
         <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
           <t>+5 KD</t>
         </is>
       </c>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
       <c r="N74" t="inlineStr">
         <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
           <t>KD KD</t>
         </is>
       </c>
-      <c r="O74" t="inlineStr">
+      <c r="P74" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="P74" t="inlineStr">
+      <c r="Q74" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="Q74" t="inlineStr">
+      <c r="R74" t="inlineStr">
         <is>
           <t>15,13</t>
         </is>
       </c>
-      <c r="R74" t="inlineStr">
+      <c r="S74" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="S74" t="inlineStr">
+      <c r="T74" t="inlineStr">
         <is>
           <t>LL</t>
         </is>
       </c>
-      <c r="V74" t="inlineStr">
+      <c r="W74" t="inlineStr">
         <is>
           <t>BS</t>
         </is>
       </c>
-      <c r="Y74" t="inlineStr">
+      <c r="Z74" t="inlineStr">
         <is>
           <t>8de90845-2c31-4181-81b1-494837824abb</t>
         </is>
       </c>
-      <c r="Z74" t="inlineStr">
+      <c r="AA74" t="inlineStr">
         <is>
           <t>4f091c07-e86b-4d56-a91f-029e8851a2bc</t>
         </is>
       </c>
-      <c r="AA74" t="inlineStr">
+      <c r="AB74" t="inlineStr">
         <is>
           <t>671ef239-098f-4d0b-bfd2-166912e226ae</t>
         </is>
@@ -6987,72 +7028,72 @@
           <t>f,N,d,DF+4,4,N+4</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr">
+      <c r="E75" t="inlineStr">
         <is>
           <t>–– Rising Kick</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr">
+      <c r="F75" t="inlineStr">
         <is>
           <t>Hell Sweep – Hell Sweep – Rising Kick</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
+      <c r="I75" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="J75" t="inlineStr">
+      <c r="K75" t="inlineStr">
         <is>
           <t>-23 -14</t>
         </is>
       </c>
-      <c r="L75" t="inlineStr">
+      <c r="M75" t="inlineStr">
         <is>
           <t>+5 KD</t>
         </is>
       </c>
-      <c r="N75" t="inlineStr">
+      <c r="O75" t="inlineStr">
         <is>
           <t>KD KD</t>
         </is>
       </c>
-      <c r="O75" t="inlineStr">
+      <c r="P75" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="P75" t="inlineStr">
+      <c r="Q75" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="Q75" t="inlineStr">
+      <c r="R75" t="inlineStr">
         <is>
           <t>15,13,14</t>
         </is>
       </c>
-      <c r="R75" t="inlineStr">
+      <c r="S75" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="S75" t="inlineStr">
+      <c r="T75" t="inlineStr">
         <is>
           <t>LLm</t>
         </is>
       </c>
-      <c r="Y75" t="inlineStr">
+      <c r="Z75" t="inlineStr">
         <is>
           <t>8438ef60-e448-466b-8dad-2a2f898d8254</t>
         </is>
       </c>
-      <c r="Z75" t="inlineStr">
+      <c r="AA75" t="inlineStr">
         <is>
           <t>d549dd8c-7b8f-47d8-9df2-a71108d1a511</t>
         </is>
       </c>
-      <c r="AA75" t="inlineStr">
+      <c r="AB75" t="inlineStr">
         <is>
           <t>8de90845-2c31-4181-81b1-494837824abb</t>
         </is>
@@ -7069,87 +7110,87 @@
           <t>f,N,d,DF+4,4,N+4,4</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr">
+      <c r="E76" t="inlineStr">
         <is>
           <t>–– Tsunami Kick</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr">
+      <c r="F76" t="inlineStr">
         <is>
           <t>Hell Sweep – Hell Sweep – Tsunami Kick</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
+      <c r="I76" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="I76" t="inlineStr">
+      <c r="J76" t="inlineStr">
         <is>
           <t>-3 -16</t>
         </is>
       </c>
-      <c r="J76" t="inlineStr">
+      <c r="K76" t="inlineStr">
         <is>
           <t>-23 -14 -3 -16</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr">
+      <c r="L76" t="inlineStr">
         <is>
           <t>+8 -5</t>
         </is>
       </c>
-      <c r="L76" t="inlineStr">
+      <c r="M76" t="inlineStr">
         <is>
           <t>+5 KD +8 -5</t>
         </is>
       </c>
-      <c r="M76" t="inlineStr">
+      <c r="N76" t="inlineStr">
         <is>
           <t>+8 -5</t>
         </is>
       </c>
-      <c r="N76" t="inlineStr">
+      <c r="O76" t="inlineStr">
         <is>
           <t>KD KD +8 -5</t>
         </is>
       </c>
-      <c r="O76" t="inlineStr">
+      <c r="P76" t="inlineStr">
         <is>
           <t>14,21</t>
         </is>
       </c>
-      <c r="P76" t="inlineStr">
+      <c r="Q76" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="Q76" t="inlineStr">
+      <c r="R76" t="inlineStr">
         <is>
           <t>15,13,14,21</t>
         </is>
       </c>
-      <c r="R76" t="inlineStr">
+      <c r="S76" t="inlineStr">
         <is>
           <t>mm</t>
         </is>
       </c>
-      <c r="S76" t="inlineStr">
+      <c r="T76" t="inlineStr">
         <is>
           <t>LLmm</t>
         </is>
       </c>
-      <c r="Y76" t="inlineStr">
+      <c r="Z76" t="inlineStr">
         <is>
           <t>839cd38f-c97a-4ee0-8ef4-8f5369ee0815</t>
         </is>
       </c>
-      <c r="Z76" t="inlineStr">
+      <c r="AA76" t="inlineStr">
         <is>
           <t>a8d4a430-cfbf-4ecf-8716-3c68d9c9fbac</t>
         </is>
       </c>
-      <c r="AA76" t="inlineStr">
+      <c r="AB76" t="inlineStr">
         <is>
           <t>8de90845-2c31-4181-81b1-494837824abb</t>
         </is>
@@ -7166,92 +7207,92 @@
           <t>f,N,d,DF+4,4,N+1</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr">
+      <c r="E77" t="inlineStr">
         <is>
           <t>–– Thunder Godfist</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr">
+      <c r="F77" t="inlineStr">
         <is>
           <t>Hell Sweep – Hell Sweep – Thunder Godfist</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
+      <c r="I77" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="I77" t="inlineStr">
+      <c r="J77" t="inlineStr">
         <is>
           <t>-12</t>
         </is>
       </c>
-      <c r="J77" t="inlineStr">
+      <c r="K77" t="inlineStr">
         <is>
           <t>-23 -14 -12</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
       <c r="L77" t="inlineStr">
         <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
           <t>+5 KD KD</t>
         </is>
       </c>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
       <c r="N77" t="inlineStr">
         <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
           <t>KD KD KD</t>
         </is>
       </c>
-      <c r="O77" t="inlineStr">
+      <c r="P77" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="P77" t="inlineStr">
+      <c r="Q77" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="Q77" t="inlineStr">
+      <c r="R77" t="inlineStr">
         <is>
           <t>15,13,21</t>
         </is>
       </c>
-      <c r="R77" t="inlineStr">
+      <c r="S77" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="S77" t="inlineStr">
+      <c r="T77" t="inlineStr">
         <is>
           <t>LLm</t>
         </is>
       </c>
-      <c r="W77" t="inlineStr">
+      <c r="X77" t="inlineStr">
         <is>
           <t>Damage will be 28 if only the Thunder Godfist hits.</t>
         </is>
       </c>
-      <c r="Y77" t="inlineStr">
+      <c r="Z77" t="inlineStr">
         <is>
           <t>614e83d4-fcab-4644-a466-f3820113dd9e</t>
         </is>
       </c>
-      <c r="Z77" t="inlineStr">
+      <c r="AA77" t="inlineStr">
         <is>
           <t>d769b421-5496-4981-a18a-f508ed792446</t>
         </is>
       </c>
-      <c r="AA77" t="inlineStr">
+      <c r="AB77" t="inlineStr">
         <is>
           <t>8de90845-2c31-4181-81b1-494837824abb</t>
         </is>
@@ -7268,92 +7309,92 @@
           <t>f,N,d,DF+4,4,4</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr">
+      <c r="E78" t="inlineStr">
         <is>
           <t>–– Hell Sweep</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr">
+      <c r="F78" t="inlineStr">
         <is>
           <t>Hell Sweep – Hell Sweep – Hell Sweep</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
+      <c r="I78" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="I78" t="inlineStr">
+      <c r="J78" t="inlineStr">
         <is>
           <t>-14</t>
         </is>
       </c>
-      <c r="J78" t="inlineStr">
+      <c r="K78" t="inlineStr">
         <is>
           <t>-23 -14 -14</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
       <c r="L78" t="inlineStr">
         <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
           <t>+5 KD KD</t>
         </is>
       </c>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
       <c r="N78" t="inlineStr">
         <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
           <t>KD KD KD</t>
         </is>
       </c>
-      <c r="O78" t="inlineStr">
+      <c r="P78" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="P78" t="inlineStr">
+      <c r="Q78" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="Q78" t="inlineStr">
+      <c r="R78" t="inlineStr">
         <is>
           <t>15,13,13</t>
         </is>
       </c>
-      <c r="R78" t="inlineStr">
+      <c r="S78" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="S78" t="inlineStr">
+      <c r="T78" t="inlineStr">
         <is>
           <t>LLL</t>
         </is>
       </c>
-      <c r="V78" t="inlineStr">
+      <c r="W78" t="inlineStr">
         <is>
           <t>BS</t>
         </is>
       </c>
-      <c r="Y78" t="inlineStr">
+      <c r="Z78" t="inlineStr">
         <is>
           <t>df5b5430-8e77-48f6-83b6-8d7561ded422</t>
         </is>
       </c>
-      <c r="Z78" t="inlineStr">
+      <c r="AA78" t="inlineStr">
         <is>
           <t>073f9e4c-be14-4c92-bb63-bf125f8be207</t>
         </is>
       </c>
-      <c r="AA78" t="inlineStr">
+      <c r="AB78" t="inlineStr">
         <is>
           <t>8de90845-2c31-4181-81b1-494837824abb</t>
         </is>
@@ -7370,72 +7411,72 @@
           <t>f,N,d,DF+4,4,4,N+4</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr">
+      <c r="E79" t="inlineStr">
         <is>
           <t>––– Rising Kick</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr">
+      <c r="F79" t="inlineStr">
         <is>
           <t>Hell Sweep – Hell Sweep – Hell Sweep – Rising Kick</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
+      <c r="I79" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="J79" t="inlineStr">
+      <c r="K79" t="inlineStr">
         <is>
           <t>-23 -14 -14</t>
         </is>
       </c>
-      <c r="L79" t="inlineStr">
+      <c r="M79" t="inlineStr">
         <is>
           <t>+5 KD KD</t>
         </is>
       </c>
-      <c r="N79" t="inlineStr">
+      <c r="O79" t="inlineStr">
         <is>
           <t>KD KD KD</t>
         </is>
       </c>
-      <c r="O79" t="inlineStr">
+      <c r="P79" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="P79" t="inlineStr">
+      <c r="Q79" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="Q79" t="inlineStr">
+      <c r="R79" t="inlineStr">
         <is>
           <t>15,13,13,14</t>
         </is>
       </c>
-      <c r="R79" t="inlineStr">
+      <c r="S79" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="S79" t="inlineStr">
+      <c r="T79" t="inlineStr">
         <is>
           <t>LLLm</t>
         </is>
       </c>
-      <c r="Y79" t="inlineStr">
+      <c r="Z79" t="inlineStr">
         <is>
           <t>13aefd14-d087-4b03-9c70-7779fb41b891</t>
         </is>
       </c>
-      <c r="Z79" t="inlineStr">
+      <c r="AA79" t="inlineStr">
         <is>
           <t>5c2d120a-2126-472c-8377-cae6ec1949dc</t>
         </is>
       </c>
-      <c r="AA79" t="inlineStr">
+      <c r="AB79" t="inlineStr">
         <is>
           <t>df5b5430-8e77-48f6-83b6-8d7561ded422</t>
         </is>
@@ -7452,87 +7493,87 @@
           <t>f,N,d,DF+4,4,4,N+4,4</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr">
+      <c r="E80" t="inlineStr">
         <is>
           <t>––– Tsunami Kick</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr">
+      <c r="F80" t="inlineStr">
         <is>
           <t>Hell Sweep – Hell Sweep – Hell Sweep – Tsunami Kick</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
+      <c r="I80" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="I80" t="inlineStr">
+      <c r="J80" t="inlineStr">
         <is>
           <t>-3 -16</t>
         </is>
       </c>
-      <c r="J80" t="inlineStr">
+      <c r="K80" t="inlineStr">
         <is>
           <t>-23 -14 -14 -3 -16</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr">
+      <c r="L80" t="inlineStr">
         <is>
           <t>+8 -5</t>
         </is>
       </c>
-      <c r="L80" t="inlineStr">
+      <c r="M80" t="inlineStr">
         <is>
           <t>+5 KD KD +8 -5</t>
         </is>
       </c>
-      <c r="M80" t="inlineStr">
+      <c r="N80" t="inlineStr">
         <is>
           <t>+8 -5</t>
         </is>
       </c>
-      <c r="N80" t="inlineStr">
+      <c r="O80" t="inlineStr">
         <is>
           <t>KD KD KD +8 -5</t>
         </is>
       </c>
-      <c r="O80" t="inlineStr">
+      <c r="P80" t="inlineStr">
         <is>
           <t>14,21</t>
         </is>
       </c>
-      <c r="P80" t="inlineStr">
+      <c r="Q80" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="Q80" t="inlineStr">
+      <c r="R80" t="inlineStr">
         <is>
           <t>15,13,13,14,21</t>
         </is>
       </c>
-      <c r="R80" t="inlineStr">
+      <c r="S80" t="inlineStr">
         <is>
           <t>mm</t>
         </is>
       </c>
-      <c r="S80" t="inlineStr">
+      <c r="T80" t="inlineStr">
         <is>
           <t>LLLmm</t>
         </is>
       </c>
-      <c r="Y80" t="inlineStr">
+      <c r="Z80" t="inlineStr">
         <is>
           <t>dd6b4fba-ebd7-46d9-822b-969ecfc3d134</t>
         </is>
       </c>
-      <c r="Z80" t="inlineStr">
+      <c r="AA80" t="inlineStr">
         <is>
           <t>1faab8f9-0b1a-438b-bc5e-321628c4aa0f</t>
         </is>
       </c>
-      <c r="AA80" t="inlineStr">
+      <c r="AB80" t="inlineStr">
         <is>
           <t>df5b5430-8e77-48f6-83b6-8d7561ded422</t>
         </is>
@@ -7549,92 +7590,92 @@
           <t>f,N,d,DF+4,4,4,N+1</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr">
+      <c r="E81" t="inlineStr">
         <is>
           <t>––– Thunder Godfist</t>
         </is>
       </c>
-      <c r="E81" t="inlineStr">
+      <c r="F81" t="inlineStr">
         <is>
           <t>Hell Sweep – Hell Sweep – Hell Sweep – Thunder Godfist</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
+      <c r="I81" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="I81" t="inlineStr">
+      <c r="J81" t="inlineStr">
         <is>
           <t>-12</t>
         </is>
       </c>
-      <c r="J81" t="inlineStr">
+      <c r="K81" t="inlineStr">
         <is>
           <t>-23 -14 -14 -12</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
       <c r="L81" t="inlineStr">
         <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
           <t>+5 KD KD KD</t>
         </is>
       </c>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
       <c r="N81" t="inlineStr">
         <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
           <t>KD KD KD KD</t>
         </is>
       </c>
-      <c r="O81" t="inlineStr">
+      <c r="P81" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="P81" t="inlineStr">
+      <c r="Q81" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="Q81" t="inlineStr">
+      <c r="R81" t="inlineStr">
         <is>
           <t>15,13,13,21</t>
         </is>
       </c>
-      <c r="R81" t="inlineStr">
+      <c r="S81" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="S81" t="inlineStr">
+      <c r="T81" t="inlineStr">
         <is>
           <t>LLLm</t>
         </is>
       </c>
-      <c r="W81" t="inlineStr">
+      <c r="X81" t="inlineStr">
         <is>
           <t>Damage will be 28 if only the Thunder Godfist hits.</t>
         </is>
       </c>
-      <c r="Y81" t="inlineStr">
+      <c r="Z81" t="inlineStr">
         <is>
           <t>32f19890-efa9-4c4a-96cf-c6cfff6168fb</t>
         </is>
       </c>
-      <c r="Z81" t="inlineStr">
+      <c r="AA81" t="inlineStr">
         <is>
           <t>7a593df9-3ea4-4514-9ab1-28e69b85b8dc</t>
         </is>
       </c>
-      <c r="AA81" t="inlineStr">
+      <c r="AB81" t="inlineStr">
         <is>
           <t>df5b5430-8e77-48f6-83b6-8d7561ded422</t>
         </is>
@@ -7651,51 +7692,46 @@
           <t>f+4</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr">
+      <c r="E82" t="inlineStr">
         <is>
           <t>Demon Axe Kick</t>
         </is>
       </c>
-      <c r="E82" t="inlineStr">
+      <c r="F82" t="inlineStr">
         <is>
           <t>Demon Axe Kick</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr">
+      <c r="H82" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr">
+      <c r="I82" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="I82" t="inlineStr">
+      <c r="J82" t="inlineStr">
         <is>
           <t>+11</t>
         </is>
       </c>
-      <c r="J82" t="inlineStr">
+      <c r="K82" t="inlineStr">
         <is>
           <t>+11</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr">
+      <c r="L82" t="inlineStr">
         <is>
           <t>+8</t>
         </is>
       </c>
-      <c r="L82" t="inlineStr">
+      <c r="M82" t="inlineStr">
         <is>
           <t>+8</t>
         </is>
       </c>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
       <c r="N82" t="inlineStr">
         <is>
           <t>KD</t>
@@ -7703,45 +7739,50 @@
       </c>
       <c r="O82" t="inlineStr">
         <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="P82" t="inlineStr">
+      <c r="Q82" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="Q82" t="inlineStr">
+      <c r="R82" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="R82" t="inlineStr">
+      <c r="S82" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="S82" t="inlineStr">
+      <c r="T82" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="V82" t="inlineStr">
+      <c r="W82" t="inlineStr">
         <is>
           <t>GB</t>
         </is>
       </c>
-      <c r="W82" t="inlineStr">
+      <c r="X82" t="inlineStr">
         <is>
           <t>Causes KS on a crouching opponent and SLD on CH.</t>
         </is>
       </c>
-      <c r="Y82" t="inlineStr">
+      <c r="Z82" t="inlineStr">
         <is>
           <t>2b24052e-6ead-4141-9dcd-9212ec22ae08</t>
         </is>
       </c>
-      <c r="Z82" t="inlineStr">
+      <c r="AA82" t="inlineStr">
         <is>
           <t>2b22bff8-e297-419f-9687-2d3fd11bf342</t>
         </is>
@@ -7765,29 +7806,29 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
+          <t>4~3</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
           <t>Demon Scissors</t>
         </is>
       </c>
-      <c r="E83" t="inlineStr">
+      <c r="F83" t="inlineStr">
         <is>
           <t>Demon Scissors</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr">
+      <c r="H83" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr">
+      <c r="I83" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
       <c r="L83" t="inlineStr">
         <is>
           <t>KD</t>
@@ -7805,40 +7846,45 @@
       </c>
       <c r="O83" t="inlineStr">
         <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="P83" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="P83" t="inlineStr">
+      <c r="Q83" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="Q83" t="inlineStr">
+      <c r="R83" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="R83" t="inlineStr">
+      <c r="S83" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="S83" t="inlineStr">
+      <c r="T83" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="W83" t="inlineStr">
+      <c r="X83" t="inlineStr">
         <is>
           <t>When the Demon Scissors whiffs the opponent Heihachi receives5 points of damage.</t>
         </is>
       </c>
-      <c r="Y83" t="inlineStr">
+      <c r="Z83" t="inlineStr">
         <is>
           <t>9379e996-1969-433c-9c6a-080c95b102f2</t>
         </is>
       </c>
-      <c r="Z83" t="inlineStr">
+      <c r="AA83" t="inlineStr">
         <is>
           <t>cd296010-10a3-4bf6-b145-36ae9dd91c58</t>
         </is>
@@ -7855,62 +7901,62 @@
           <t>d+4</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr">
+      <c r="E84" t="inlineStr">
         <is>
           <t>Geta Stomp</t>
         </is>
       </c>
-      <c r="E84" t="inlineStr">
+      <c r="F84" t="inlineStr">
         <is>
           <t>Geta Stomp</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr">
+      <c r="H84" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
+      <c r="I84" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="O84" t="inlineStr">
+      <c r="P84" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="P84" t="inlineStr">
+      <c r="Q84" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="Q84" t="inlineStr">
+      <c r="R84" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="R84" t="inlineStr">
+      <c r="S84" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="S84" t="inlineStr">
+      <c r="T84" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="W84" t="inlineStr">
+      <c r="X84" t="inlineStr">
         <is>
           <t>Move can only be done when the opponent is knocked of his feet.</t>
         </is>
       </c>
-      <c r="Y84" t="inlineStr">
+      <c r="Z84" t="inlineStr">
         <is>
           <t>94acdeb7-0477-4e1e-85c2-2db0d91ff8b0</t>
         </is>
       </c>
-      <c r="Z84" t="inlineStr">
+      <c r="AA84" t="inlineStr">
         <is>
           <t>b788230d-dc12-41e9-b8e9-1b3e7fe7f202</t>
         </is>
@@ -7927,47 +7973,47 @@
           <t>b,b,N+3+4</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr">
+      <c r="E85" t="inlineStr">
         <is>
           <t>Shadow Step</t>
         </is>
       </c>
-      <c r="E85" t="inlineStr">
+      <c r="F85" t="inlineStr">
         <is>
           <t>Shadow Step</t>
         </is>
       </c>
-      <c r="O85" t="inlineStr">
+      <c r="P85" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="P85" t="inlineStr">
+      <c r="Q85" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Q85" t="inlineStr">
+      <c r="R85" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="R85" t="inlineStr">
+      <c r="S85" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="S85" t="inlineStr">
+      <c r="T85" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Y85" t="inlineStr">
+      <c r="Z85" t="inlineStr">
         <is>
           <t>dee0cf29-d794-47dd-ba10-3892d4998923</t>
         </is>
       </c>
-      <c r="Z85" t="inlineStr">
+      <c r="AA85" t="inlineStr">
         <is>
           <t>efba7a2e-fb22-4e3c-8840-2c08ce17fa6e</t>
         </is>
@@ -7984,47 +8030,47 @@
           <t>2+3+4</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr">
+      <c r="E86" t="inlineStr">
         <is>
           <t>Auger Taunt</t>
         </is>
       </c>
-      <c r="E86" t="inlineStr">
+      <c r="F86" t="inlineStr">
         <is>
           <t>Auger Taunt</t>
         </is>
       </c>
-      <c r="O86" t="inlineStr">
+      <c r="P86" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="P86" t="inlineStr">
+      <c r="Q86" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Q86" t="inlineStr">
+      <c r="R86" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="R86" t="inlineStr">
+      <c r="S86" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="S86" t="inlineStr">
+      <c r="T86" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Y86" t="inlineStr">
+      <c r="Z86" t="inlineStr">
         <is>
           <t>a50232da-bfb3-4233-9a67-fedf01a87e85</t>
         </is>
       </c>
-      <c r="Z86" t="inlineStr">
+      <c r="AA86" t="inlineStr">
         <is>
           <t>4dcc8644-7a10-4584-a44c-ed10e3b62b44</t>
         </is>
@@ -8056,125 +8102,130 @@
       </c>
       <c r="D89" s="1" t="inlineStr">
         <is>
+          <t>Alt Commands Full</t>
+        </is>
+      </c>
+      <c r="E89" s="1" t="inlineStr">
+        <is>
           <t>Move Name</t>
         </is>
       </c>
-      <c r="E89" s="1" t="inlineStr">
+      <c r="F89" s="1" t="inlineStr">
         <is>
           <t>Move Name Full</t>
         </is>
       </c>
-      <c r="F89" s="1" t="inlineStr">
+      <c r="G89" s="1" t="inlineStr">
         <is>
           <t>To Stance</t>
         </is>
       </c>
-      <c r="G89" s="1" t="inlineStr">
+      <c r="H89" s="1" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
-      <c r="H89" s="1" t="inlineStr">
+      <c r="I89" s="1" t="inlineStr">
         <is>
           <t>Speed Full</t>
         </is>
       </c>
-      <c r="I89" s="1" t="inlineStr">
+      <c r="J89" s="1" t="inlineStr">
         <is>
           <t>Block Adv</t>
         </is>
       </c>
-      <c r="J89" s="1" t="inlineStr">
+      <c r="K89" s="1" t="inlineStr">
         <is>
           <t>Block Adv Full</t>
         </is>
       </c>
-      <c r="K89" s="1" t="inlineStr">
+      <c r="L89" s="1" t="inlineStr">
         <is>
           <t>Hit Adv</t>
         </is>
       </c>
-      <c r="L89" s="1" t="inlineStr">
+      <c r="M89" s="1" t="inlineStr">
         <is>
           <t>Hit Adv Full</t>
         </is>
       </c>
-      <c r="M89" s="1" t="inlineStr">
+      <c r="N89" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv</t>
         </is>
       </c>
-      <c r="N89" s="1" t="inlineStr">
+      <c r="O89" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv Full</t>
         </is>
       </c>
-      <c r="O89" s="1" t="inlineStr">
+      <c r="P89" s="1" t="inlineStr">
         <is>
           <t>Damage</t>
         </is>
       </c>
-      <c r="P89" s="1" t="inlineStr">
+      <c r="Q89" s="1" t="inlineStr">
         <is>
           <t>Damage Sum</t>
         </is>
       </c>
-      <c r="Q89" s="1" t="inlineStr">
+      <c r="R89" s="1" t="inlineStr">
         <is>
           <t>Damage Full</t>
         </is>
       </c>
-      <c r="R89" s="1" t="inlineStr">
+      <c r="S89" s="1" t="inlineStr">
         <is>
           <t>Hit Range</t>
         </is>
       </c>
-      <c r="S89" s="1" t="inlineStr">
+      <c r="T89" s="1" t="inlineStr">
         <is>
           <t>Hit Range Full</t>
         </is>
       </c>
-      <c r="T89" s="1" t="inlineStr">
+      <c r="U89" s="1" t="inlineStr">
         <is>
           <t>Throw Type</t>
         </is>
       </c>
-      <c r="U89" s="1" t="inlineStr">
+      <c r="V89" s="1" t="inlineStr">
         <is>
           <t>Throw Escape</t>
         </is>
       </c>
-      <c r="V89" s="1" t="inlineStr">
+      <c r="W89" s="1" t="inlineStr">
         <is>
           <t>Properties</t>
         </is>
       </c>
-      <c r="W89" s="1" t="inlineStr">
+      <c r="X89" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="X89" s="1" t="inlineStr">
+      <c r="Y89" s="1" t="inlineStr">
         <is>
           <t>Taggable</t>
         </is>
       </c>
-      <c r="Y89" s="1" t="inlineStr">
+      <c r="Z89" s="1" t="inlineStr">
         <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="Z89" s="1" t="inlineStr">
+      <c r="AA89" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="AA89" s="1" t="inlineStr">
+      <c r="AB89" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="AB89" s="1" t="inlineStr">
+      <c r="AC89" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
@@ -8191,31 +8242,26 @@
           <t>d+1+4</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr">
+      <c r="E90" t="inlineStr">
         <is>
           <t>Demon Tile Splitter</t>
         </is>
       </c>
-      <c r="E90" t="inlineStr">
+      <c r="F90" t="inlineStr">
         <is>
           <t>Demon Tile Splitter</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr">
+      <c r="H90" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr">
+      <c r="I90" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
       <c r="L90" t="inlineStr">
         <is>
           <t>KD</t>
@@ -8233,40 +8279,45 @@
       </c>
       <c r="O90" t="inlineStr">
         <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="P90" t="inlineStr">
+        <is>
           <t>70</t>
         </is>
       </c>
-      <c r="P90" t="inlineStr">
+      <c r="Q90" t="inlineStr">
         <is>
           <t>70</t>
         </is>
       </c>
-      <c r="Q90" t="inlineStr">
+      <c r="R90" t="inlineStr">
         <is>
           <t>70</t>
         </is>
       </c>
-      <c r="R90" t="inlineStr">
+      <c r="S90" t="inlineStr">
         <is>
           <t>!</t>
         </is>
       </c>
-      <c r="S90" t="inlineStr">
+      <c r="T90" t="inlineStr">
         <is>
           <t>!</t>
         </is>
       </c>
-      <c r="W90" t="inlineStr">
+      <c r="X90" t="inlineStr">
         <is>
           <t>Heihachi will automaticly reverse any right kick attack during the Demon Tile Splitter animation.</t>
         </is>
       </c>
-      <c r="Y90" t="inlineStr">
+      <c r="Z90" t="inlineStr">
         <is>
           <t>3ee1c731-c510-4ce8-abfe-895f352df4cf</t>
         </is>
       </c>
-      <c r="Z90" t="inlineStr">
+      <c r="AA90" t="inlineStr">
         <is>
           <t>37d96e68-85ef-4dc9-a8e4-fdec56988479</t>
         </is>
@@ -8298,125 +8349,130 @@
       </c>
       <c r="D93" s="1" t="inlineStr">
         <is>
+          <t>Alt Commands Full</t>
+        </is>
+      </c>
+      <c r="E93" s="1" t="inlineStr">
+        <is>
           <t>Move Name</t>
         </is>
       </c>
-      <c r="E93" s="1" t="inlineStr">
+      <c r="F93" s="1" t="inlineStr">
         <is>
           <t>Move Name Full</t>
         </is>
       </c>
-      <c r="F93" s="1" t="inlineStr">
+      <c r="G93" s="1" t="inlineStr">
         <is>
           <t>To Stance</t>
         </is>
       </c>
-      <c r="G93" s="1" t="inlineStr">
+      <c r="H93" s="1" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
-      <c r="H93" s="1" t="inlineStr">
+      <c r="I93" s="1" t="inlineStr">
         <is>
           <t>Speed Full</t>
         </is>
       </c>
-      <c r="I93" s="1" t="inlineStr">
+      <c r="J93" s="1" t="inlineStr">
         <is>
           <t>Block Adv</t>
         </is>
       </c>
-      <c r="J93" s="1" t="inlineStr">
+      <c r="K93" s="1" t="inlineStr">
         <is>
           <t>Block Adv Full</t>
         </is>
       </c>
-      <c r="K93" s="1" t="inlineStr">
+      <c r="L93" s="1" t="inlineStr">
         <is>
           <t>Hit Adv</t>
         </is>
       </c>
-      <c r="L93" s="1" t="inlineStr">
+      <c r="M93" s="1" t="inlineStr">
         <is>
           <t>Hit Adv Full</t>
         </is>
       </c>
-      <c r="M93" s="1" t="inlineStr">
+      <c r="N93" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv</t>
         </is>
       </c>
-      <c r="N93" s="1" t="inlineStr">
+      <c r="O93" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv Full</t>
         </is>
       </c>
-      <c r="O93" s="1" t="inlineStr">
+      <c r="P93" s="1" t="inlineStr">
         <is>
           <t>Damage</t>
         </is>
       </c>
-      <c r="P93" s="1" t="inlineStr">
+      <c r="Q93" s="1" t="inlineStr">
         <is>
           <t>Damage Sum</t>
         </is>
       </c>
-      <c r="Q93" s="1" t="inlineStr">
+      <c r="R93" s="1" t="inlineStr">
         <is>
           <t>Damage Full</t>
         </is>
       </c>
-      <c r="R93" s="1" t="inlineStr">
+      <c r="S93" s="1" t="inlineStr">
         <is>
           <t>Hit Range</t>
         </is>
       </c>
-      <c r="S93" s="1" t="inlineStr">
+      <c r="T93" s="1" t="inlineStr">
         <is>
           <t>Hit Range Full</t>
         </is>
       </c>
-      <c r="T93" s="1" t="inlineStr">
+      <c r="U93" s="1" t="inlineStr">
         <is>
           <t>Throw Type</t>
         </is>
       </c>
-      <c r="U93" s="1" t="inlineStr">
+      <c r="V93" s="1" t="inlineStr">
         <is>
           <t>Throw Escape</t>
         </is>
       </c>
-      <c r="V93" s="1" t="inlineStr">
+      <c r="W93" s="1" t="inlineStr">
         <is>
           <t>Properties</t>
         </is>
       </c>
-      <c r="W93" s="1" t="inlineStr">
+      <c r="X93" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="X93" s="1" t="inlineStr">
+      <c r="Y93" s="1" t="inlineStr">
         <is>
           <t>Taggable</t>
         </is>
       </c>
-      <c r="Y93" s="1" t="inlineStr">
+      <c r="Z93" s="1" t="inlineStr">
         <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="Z93" s="1" t="inlineStr">
+      <c r="AA93" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="AA93" s="1" t="inlineStr">
+      <c r="AB93" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="AB93" s="1" t="inlineStr">
+      <c r="AC93" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
@@ -8433,42 +8489,42 @@
           <t>df+3,2,2,4,4,1,4,1,2,4</t>
         </is>
       </c>
-      <c r="O94" t="inlineStr">
+      <c r="P94" t="inlineStr">
         <is>
           <t>17,5,6,8,8,5,10,5,6,35</t>
         </is>
       </c>
-      <c r="P94" t="inlineStr">
+      <c r="Q94" t="inlineStr">
         <is>
           <t>105</t>
         </is>
       </c>
-      <c r="Q94" t="inlineStr">
+      <c r="R94" t="inlineStr">
         <is>
           <t>17,5,6,8,8,5,10,5,6,35</t>
         </is>
       </c>
-      <c r="R94" t="inlineStr">
+      <c r="S94" t="inlineStr">
         <is>
           <t>mhhLLmhhmm</t>
         </is>
       </c>
-      <c r="S94" t="inlineStr">
+      <c r="T94" t="inlineStr">
         <is>
           <t>mhhLLmhhmm</t>
         </is>
       </c>
-      <c r="Y94" t="inlineStr">
+      <c r="Z94" t="inlineStr">
         <is>
           <t>5e401bff-867a-4231-89fe-31140fb8cfa3</t>
         </is>
       </c>
-      <c r="Z94" t="inlineStr">
+      <c r="AA94" t="inlineStr">
         <is>
           <t>5e401bff-867a-4231-89fe-31140fb8cfa3</t>
         </is>
       </c>
-      <c r="AB94" t="inlineStr">
+      <c r="AC94" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -8485,42 +8541,42 @@
           <t>df+3,2,2,4,4,1,4,1,2,1</t>
         </is>
       </c>
-      <c r="O95" t="inlineStr">
+      <c r="P95" t="inlineStr">
         <is>
           <t>17,5,6,8,8,5,10,5,6,30</t>
         </is>
       </c>
-      <c r="P95" t="inlineStr">
+      <c r="Q95" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="Q95" t="inlineStr">
+      <c r="R95" t="inlineStr">
         <is>
           <t>17,5,6,8,8,5,10,5,6,30</t>
         </is>
       </c>
-      <c r="R95" t="inlineStr">
+      <c r="S95" t="inlineStr">
         <is>
           <t>mhhLLmhhmm</t>
         </is>
       </c>
-      <c r="S95" t="inlineStr">
+      <c r="T95" t="inlineStr">
         <is>
           <t>mhhLLmhhmm</t>
         </is>
       </c>
-      <c r="Y95" t="inlineStr">
+      <c r="Z95" t="inlineStr">
         <is>
           <t>4843994c-4a83-4e19-a59d-b3e33a4b6216</t>
         </is>
       </c>
-      <c r="Z95" t="inlineStr">
+      <c r="AA95" t="inlineStr">
         <is>
           <t>4843994c-4a83-4e19-a59d-b3e33a4b6216</t>
         </is>
       </c>
-      <c r="AB95" t="inlineStr">
+      <c r="AC95" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -8537,42 +8593,42 @@
           <t>df+3,2,2,4,4,1,2,1,2,1</t>
         </is>
       </c>
-      <c r="O96" t="inlineStr">
+      <c r="P96" t="inlineStr">
         <is>
           <t>17,5,6,8,8,5,5,8,21,25</t>
         </is>
       </c>
-      <c r="P96" t="inlineStr">
+      <c r="Q96" t="inlineStr">
         <is>
           <t>108</t>
         </is>
       </c>
-      <c r="Q96" t="inlineStr">
+      <c r="R96" t="inlineStr">
         <is>
           <t>17,5,6,8,8,5,5,8,21,25</t>
         </is>
       </c>
-      <c r="R96" t="inlineStr">
+      <c r="S96" t="inlineStr">
         <is>
           <t>mhhLLmhmmm</t>
         </is>
       </c>
-      <c r="S96" t="inlineStr">
+      <c r="T96" t="inlineStr">
         <is>
           <t>mhhLLmhmmm</t>
         </is>
       </c>
-      <c r="Y96" t="inlineStr">
+      <c r="Z96" t="inlineStr">
         <is>
           <t>b75ce8db-3ddd-40cc-b908-e15c334e3eff</t>
         </is>
       </c>
-      <c r="Z96" t="inlineStr">
+      <c r="AA96" t="inlineStr">
         <is>
           <t>b75ce8db-3ddd-40cc-b908-e15c334e3eff</t>
         </is>
       </c>
-      <c r="AB96" t="inlineStr">
+      <c r="AC96" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -8589,42 +8645,42 @@
           <t>f,f+2,1,2,2,3,4,4,1,2,1</t>
         </is>
       </c>
-      <c r="O97" t="inlineStr">
+      <c r="P97" t="inlineStr">
         <is>
           <t>7,8,6,7,6,11,5,5,8,30</t>
         </is>
       </c>
-      <c r="P97" t="inlineStr">
+      <c r="Q97" t="inlineStr">
         <is>
           <t>93</t>
         </is>
       </c>
-      <c r="Q97" t="inlineStr">
+      <c r="R97" t="inlineStr">
         <is>
           <t>7,8,6,7,6,11,5,5,8,30</t>
         </is>
       </c>
-      <c r="R97" t="inlineStr">
+      <c r="S97" t="inlineStr">
         <is>
           <t>hhhhmmlhmm</t>
         </is>
       </c>
-      <c r="S97" t="inlineStr">
+      <c r="T97" t="inlineStr">
         <is>
           <t>hhhhmmlhmm</t>
         </is>
       </c>
-      <c r="Y97" t="inlineStr">
+      <c r="Z97" t="inlineStr">
         <is>
           <t>59b8bd40-2cec-44af-a5be-02b8f9c50b3c</t>
         </is>
       </c>
-      <c r="Z97" t="inlineStr">
+      <c r="AA97" t="inlineStr">
         <is>
           <t>59b8bd40-2cec-44af-a5be-02b8f9c50b3c</t>
         </is>
       </c>
-      <c r="AB97" t="inlineStr">
+      <c r="AC97" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
